--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -919,7 +919,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -990,7 +989,6 @@
       </c>
       <c r="M5" s="71" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -2271,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2359,624 +2357,879 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="52" t="n">
-        <v>1</v>
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
       </c>
       <c r="B4" s="52" t="inlineStr">
         <is>
-          <t>NV01</t>
+          <t>Mã NV</t>
         </is>
       </c>
       <c r="C4" s="53" t="inlineStr">
         <is>
-          <t>Hoàng Ngọc Hà</t>
+          <t>Họ Và Tên Thợ Gia Công</t>
         </is>
       </c>
       <c r="D4" s="53" t="inlineStr">
         <is>
-          <t>Máy tiện OKUMA</t>
-        </is>
-      </c>
-      <c r="E4" s="54">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="55">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C4, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G4" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C4, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H4" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C4, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I4" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C4, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J4" s="56">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C4, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K4" s="57">
-        <f>I4-J4</f>
-        <v/>
+          <t>Vị Trí / Máy Đảm Nhiệm</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>Số Ca Làm Việc</t>
+        </is>
+      </c>
+      <c r="F4" s="55" t="inlineStr">
+        <is>
+          <t>Tổng Giờ Máy (h)</t>
+        </is>
+      </c>
+      <c r="G4" s="56" t="inlineStr">
+        <is>
+          <t>Tổng SL Đạt (OK)</t>
+        </is>
+      </c>
+      <c r="H4" s="56" t="inlineStr">
+        <is>
+          <t>Tổng SL Hỏng (NG)</t>
+        </is>
+      </c>
+      <c r="I4" s="56" t="inlineStr">
+        <is>
+          <t>Tiền Khoán Tạm Tính (VNĐ)</t>
+        </is>
+      </c>
+      <c r="J4" s="56" t="inlineStr">
+        <is>
+          <t>Tiền Đủ Điều Kiện (KCS Duyệt)</t>
+        </is>
+      </c>
+      <c r="K4" s="57" t="inlineStr">
+        <is>
+          <t>Trừ Phạt Phế Phẩm (VNĐ)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Lương Thực Lĩnh Đã Chốt (VNĐ)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Trạng Thái Chốt Lương</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ký Nhận</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="58" t="inlineStr">
         <is>
-          <t>NV02</t>
+          <t>NV01</t>
         </is>
       </c>
       <c r="C5" s="59" t="inlineStr">
         <is>
-          <t>Nguyễn Trung Đông</t>
+          <t>Hoàng Ngọc Hà</t>
         </is>
       </c>
       <c r="D5" s="59" t="inlineStr">
         <is>
-          <t>Máy tiện FUJI</t>
-        </is>
-      </c>
-      <c r="E5" s="60">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="61">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C5, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G5" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C5, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H5" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C5, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I5" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C5, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J5" s="62">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C5, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K5" s="57">
-        <f>I5-J5</f>
-        <v/>
-      </c>
+          <t>M01 - Máy tiện FUJI</t>
+        </is>
+      </c>
+      <c r="E5" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="61" t="n">
+        <v>80</v>
+      </c>
+      <c r="G5" s="62" t="n">
+        <v>160</v>
+      </c>
+      <c r="H5" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J5" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="K5" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>NV03</t>
+          <t>NV02</t>
         </is>
       </c>
       <c r="C6" s="53" t="inlineStr">
         <is>
-          <t>Phùng Đình Hùng</t>
+          <t>Nguyễn Trung Đông</t>
         </is>
       </c>
       <c r="D6" s="53" t="inlineStr">
         <is>
-          <t>Máy tiện Tiện T1516</t>
-        </is>
-      </c>
-      <c r="E6" s="54">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="55">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C6, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G6" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C6, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H6" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C6, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I6" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C6, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J6" s="56">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C6, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K6" s="57">
-        <f>I6-J6</f>
-        <v/>
-      </c>
+          <t>M02 - Máy tiện OKUMA</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>80</v>
+      </c>
+      <c r="G6" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="H6" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="56" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J6" s="56" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="K6" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>NV04</t>
+          <t>NV03</t>
         </is>
       </c>
       <c r="C7" s="59" t="inlineStr">
         <is>
-          <t>Vũ Tiến Thuận</t>
+          <t>Phùng Đình Hùng</t>
         </is>
       </c>
       <c r="D7" s="59" t="inlineStr">
         <is>
-          <t>Máy tiện Tiện T1517</t>
-        </is>
-      </c>
-      <c r="E7" s="60">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="61">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C7, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G7" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C7, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H7" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C7, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I7" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C7, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J7" s="62">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C7, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K7" s="57">
-        <f>I7-J7</f>
-        <v/>
-      </c>
+          <t>M03 - Máy tiện CNC1</t>
+        </is>
+      </c>
+      <c r="E7" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="61" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" s="62" t="n">
+        <v>160</v>
+      </c>
+      <c r="H7" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J7" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>NV05</t>
+          <t>NV04</t>
         </is>
       </c>
       <c r="C8" s="53" t="inlineStr">
         <is>
-          <t>Nguyễn Mạnh Hà</t>
+          <t>Vũ Tiến Thuận</t>
         </is>
       </c>
       <c r="D8" s="53" t="inlineStr">
         <is>
-          <t>Máy Phay OKK1</t>
-        </is>
-      </c>
-      <c r="E8" s="54">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="55">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C8, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G8" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C8, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H8" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C8, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I8" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C8, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J8" s="56">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C8, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K8" s="57">
-        <f>I8-J8</f>
-        <v/>
-      </c>
+          <t>M04 - Máy tiện CNC2</t>
+        </is>
+      </c>
+      <c r="E8" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="55" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="H8" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="56" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J8" s="56" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="K8" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="58" t="inlineStr">
         <is>
-          <t>NV06</t>
+          <t>NV05</t>
         </is>
       </c>
       <c r="C9" s="59" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thanh</t>
+          <t>Nguyễn Mạnh Hà</t>
         </is>
       </c>
       <c r="D9" s="59" t="inlineStr">
         <is>
-          <t>Máy tiện OKUMA</t>
-        </is>
-      </c>
-      <c r="E9" s="60">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="61">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C9, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G9" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C9, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H9" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C9, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I9" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C9, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J9" s="62">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C9, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K9" s="57">
-        <f>I9-J9</f>
-        <v/>
-      </c>
+          <t>M05 - Máy tiện T630</t>
+        </is>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="61" t="n">
+        <v>80</v>
+      </c>
+      <c r="G9" s="62" t="n">
+        <v>160</v>
+      </c>
+      <c r="H9" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J9" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="K9" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>NV07</t>
+          <t>NV06</t>
         </is>
       </c>
       <c r="C10" s="53" t="inlineStr">
         <is>
-          <t>Phùng Gia Phúc</t>
+          <t>Nguyễn Văn Thanh</t>
         </is>
       </c>
       <c r="D10" s="53" t="inlineStr">
         <is>
-          <t>Máy Phay OKK3</t>
-        </is>
-      </c>
-      <c r="E10" s="54">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="55">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C10, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G10" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C10, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H10" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C10, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I10" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C10, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J10" s="56">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C10, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K10" s="57">
-        <f>I10-J10</f>
-        <v/>
-      </c>
+          <t>M06 - Máy tiện T1516</t>
+        </is>
+      </c>
+      <c r="E10" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="55" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="H10" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="56" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="J10" s="56" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="K10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="58" t="inlineStr">
         <is>
-          <t>NV08</t>
+          <t>NV07</t>
         </is>
       </c>
       <c r="C11" s="59" t="inlineStr">
         <is>
-          <t>Trần Văn Dũng</t>
+          <t>Phùng Gia Phúc</t>
         </is>
       </c>
       <c r="D11" s="59" t="inlineStr">
         <is>
-          <t>Máy Phay CNC1</t>
-        </is>
-      </c>
-      <c r="E11" s="60">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="61">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C11, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G11" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C11, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H11" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C11, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I11" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C11, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J11" s="62">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C11, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K11" s="57">
-        <f>I11-J11</f>
-        <v/>
-      </c>
+          <t>M07 - Máy Phay OKK1</t>
+        </is>
+      </c>
+      <c r="E11" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="61" t="n">
+        <v>80</v>
+      </c>
+      <c r="G11" s="62" t="n">
+        <v>160</v>
+      </c>
+      <c r="H11" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="62" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="J11" s="62" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="K11" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>NV09</t>
+          <t>NV08</t>
         </is>
       </c>
       <c r="C12" s="53" t="inlineStr">
         <is>
-          <t>Trần Đăng Ninh</t>
+          <t>Trần Văn Dũng</t>
         </is>
       </c>
       <c r="D12" s="53" t="inlineStr">
         <is>
-          <t>Máy Phay CNC2</t>
-        </is>
-      </c>
-      <c r="E12" s="54">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="55">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C12, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G12" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C12, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H12" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C12, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I12" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C12, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J12" s="56">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C12, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K12" s="57">
-        <f>I12-J12</f>
-        <v/>
-      </c>
+          <t>M08 - Máy Phay OKK2</t>
+        </is>
+      </c>
+      <c r="E12" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="55" t="n">
+        <v>80</v>
+      </c>
+      <c r="G12" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="H12" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="56" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="J12" s="56" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="K12" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="58" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>NV09</t>
+        </is>
+      </c>
+      <c r="C13" s="59" t="inlineStr">
+        <is>
+          <t>Trần Đăng Ninh</t>
+        </is>
+      </c>
+      <c r="D13" s="59" t="inlineStr">
+        <is>
+          <t>M09 - Máy Phay OKK3</t>
+        </is>
+      </c>
+      <c r="E13" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="58" t="inlineStr">
-        <is>
-          <t>NV10</t>
-        </is>
-      </c>
-      <c r="C13" s="59" t="inlineStr">
-        <is>
-          <t>Phạm Văn Tráng</t>
-        </is>
-      </c>
-      <c r="D13" s="59" t="inlineStr">
-        <is>
-          <t>Máy Phay OKK1</t>
-        </is>
-      </c>
-      <c r="E13" s="60">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="61">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C13, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G13" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C13, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H13" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C13, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I13" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C13, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J13" s="62">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C13, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K13" s="57">
-        <f>I13-J13</f>
-        <v/>
-      </c>
+      <c r="F13" s="61" t="n">
+        <v>80</v>
+      </c>
+      <c r="G13" s="62" t="n">
+        <v>160</v>
+      </c>
+      <c r="H13" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="62" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="J13" s="62" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="K13" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>NV11</t>
+          <t>NV10</t>
         </is>
       </c>
       <c r="C14" s="53" t="inlineStr">
         <is>
-          <t>Đặng Ngọc Long</t>
+          <t>Phạm Văn Tráng</t>
         </is>
       </c>
       <c r="D14" s="53" t="inlineStr">
         <is>
-          <t>Máy tiện FUJI</t>
-        </is>
-      </c>
-      <c r="E14" s="54">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="55">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C14, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G14" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C14, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H14" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C14, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I14" s="56">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C14, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J14" s="56">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C14, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K14" s="57">
-        <f>I14-J14</f>
-        <v/>
-      </c>
+          <t>M10 - Máy Phay CNC1</t>
+        </is>
+      </c>
+      <c r="E14" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="55" t="n">
+        <v>80</v>
+      </c>
+      <c r="G14" s="56" t="n">
+        <v>160</v>
+      </c>
+      <c r="H14" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="56" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J14" s="56" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="K14" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="58" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>NV11</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="inlineStr">
+        <is>
+          <t>Phùng Công Thắng</t>
+        </is>
+      </c>
+      <c r="D15" s="59" t="inlineStr">
+        <is>
+          <t>M11 - Máy Phay CNC2</t>
+        </is>
+      </c>
+      <c r="E15" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="61" t="n">
+        <v>80</v>
+      </c>
+      <c r="G15" s="62" t="n">
+        <v>160</v>
+      </c>
+      <c r="H15" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J15" s="62" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="K15" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>NV12</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
-        <is>
-          <t>Phùng Công Thắng</t>
-        </is>
-      </c>
-      <c r="D15" s="59" t="inlineStr">
-        <is>
-          <t>Máy Cắt Dây DK7745</t>
-        </is>
-      </c>
-      <c r="E15" s="60">
-        <f>COUNTIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="61">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C15, '07_Quet_Ma_Nhat_Ky_Ca'!$O:$O)</f>
-        <v/>
-      </c>
-      <c r="G15" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C15, '07_Quet_Ma_Nhat_Ky_Ca'!$M:$M)</f>
-        <v/>
-      </c>
-      <c r="H15" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C15, '07_Quet_Ma_Nhat_Ky_Ca'!$N:$N)</f>
-        <v/>
-      </c>
-      <c r="I15" s="62">
-        <f>SUMIF('07_Quet_Ma_Nhat_Ky_Ca'!$D:$D, C15, '07_Quet_Ma_Nhat_Ky_Ca'!$P:$P)</f>
-        <v/>
-      </c>
-      <c r="J15" s="62">
-        <f>SUMIFS('08_Kiem_Soat_Chat_Luong_QA'!$I:$I, '08_Kiem_Soat_Chat_Luong_QA'!$G:$G, C15, '08_Kiem_Soat_Chat_Luong_QA'!$J:$J, "Lỗi Thao Tác Thợ") * 100000</f>
-        <v/>
-      </c>
-      <c r="K15" s="57">
-        <f>I15-J15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG QUỸ LƯƠNG KHOÁN</t>
-        </is>
-      </c>
-      <c r="B16" s="72" t="n"/>
-      <c r="C16" s="72" t="n"/>
-      <c r="D16" s="73" t="n"/>
-      <c r="E16" s="23">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="63">
-        <f>SUM(F4:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="24">
-        <f>SUM(G4:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="24">
-        <f>SUM(H4:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="24">
-        <f>SUM(I4:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="24">
-        <f>SUM(J4:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="24">
-        <f>SUM(K4:K15)</f>
-        <v/>
-      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Sam</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>M12 - Máy Phay OIGO</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="63" t="n">
+        <v>80</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>152</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>5698992</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>5698992</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5698992</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NV13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Trần Văn Quỳnh</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>M13 - Máy Phay YM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>72</v>
+      </c>
+      <c r="G17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NV14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Đinh Văn Nhận</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>M15 - Máy Khoan cần Yoshida</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G18" t="n">
+        <v>160</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NV15</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Đặng Ngọc Long</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>M16 - Máy Cắt Dây DK7745</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>72</v>
+      </c>
+      <c r="G19" t="n">
+        <v>160</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Đã chốt lương kỳ này</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG QUỸ LƯƠNG KHOÁN (15 THỢ)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20">
+        <f>SUM(E5:E19)</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>SUM(F5:F19)</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>SUM(G5:G19)</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>SUM(H5:H19)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>SUM(I5:I19)</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>SUM(J5:J19)</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>SUM(K5:K19)</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>SUM(L5:L19)</f>
+        <v/>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>KHỚP 100% NHẬT KÝ ĐÃ KHÓA</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3011,7 +3264,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -3408,7 +3660,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -13496,9 +13747,6 @@
           <t>TỔNG HỢP TOÀN NHÀ MÁY (17 MÁY)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" s="84" t="n">
         <v>33.5</v>
       </c>

--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -1072,37 +1072,32 @@
           <t>Sealing strip, below / above (Thép hợp kim chịu mòn)</t>
         </is>
       </c>
-      <c r="D9" s="13">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B9, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F9" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B9, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G9" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B9, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H9" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B9, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I9" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B9, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D9" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>100</v>
       </c>
       <c r="J9" s="15">
-        <f>IF(E9=0, 0, G9/E9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="11">
-        <f>IF(G9&gt;=E9, "Đã chuyển đủ 100%", IF(F9&gt;=E9, "Xong xưởng - Chờ chuyển", IF(F9&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G9/E9</f>
+        <v/>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -1124,37 +1119,32 @@
           <t>Cánh xoắn đùn ISHIZUE (355Dw900, 318Dw800, 216Dw650...)</t>
         </is>
       </c>
-      <c r="D10" s="18">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B10, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F10" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B10, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G10" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B10, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H10" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B10, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I10" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B10, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D10" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>850</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>450</v>
       </c>
       <c r="J10" s="20">
-        <f>IF(E10=0, 0, G10/E10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="16">
-        <f>IF(G10&gt;=E10, "Đã chuyển đủ 100%", IF(F10&gt;=E10, "Xong xưởng - Chờ chuyển", IF(F10&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G10/E10</f>
+        <v/>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
@@ -1176,37 +1166,32 @@
           <t>Mẫu thử cơ tính CR, Mẫu kéo nén ASTM</t>
         </is>
       </c>
-      <c r="D11" s="13">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B11, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F11" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B11, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G11" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B11, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H11" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B11, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I11" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B11, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D11" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>410</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>120</v>
       </c>
       <c r="J11" s="15">
-        <f>IF(E11=0, 0, G11/E11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="11">
-        <f>IF(G11&gt;=E11, "Đã chuyển đủ 100%", IF(F11&gt;=E11, "Xong xưởng - Chờ chuyển", IF(F11&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G11/E11</f>
+        <v/>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -1228,37 +1213,32 @@
           <t>Ốp dao nhào trên (Bộ bên trái / bên phải)</t>
         </is>
       </c>
-      <c r="D12" s="18">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B12, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F12" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B12, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G12" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B12, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H12" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B12, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I12" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B12, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D12" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>380</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>310</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>280</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>100</v>
       </c>
       <c r="J12" s="20">
-        <f>IF(E12=0, 0, G12/E12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="16">
-        <f>IF(G12&gt;=E12, "Đã chuyển đủ 100%", IF(F12&gt;=E12, "Xong xưởng - Chờ chuyển", IF(F12&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G12/E12</f>
+        <v/>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1280,37 +1260,32 @@
           <t>Bi đúc hợp kim cắt dây &amp; mài từ</t>
         </is>
       </c>
-      <c r="D13" s="13">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B13, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F13" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B13, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B13, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H13" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B13, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I13" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B13, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>40</v>
       </c>
       <c r="J13" s="15">
-        <f>IF(E13=0, 0, G13/E13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="11">
-        <f>IF(G13&gt;=E13, "Đã chuyển đủ 100%", IF(F13&gt;=E13, "Xong xưởng - Chờ chuyển", IF(F13&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G13/E13</f>
+        <v/>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -1332,37 +1307,32 @@
           <t>Thanh đập đá vôi (2240x510x145 - Thép Mn13)</t>
         </is>
       </c>
-      <c r="D14" s="18">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B14, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F14" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B14, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G14" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B14, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H14" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B14, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I14" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B14, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D14" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>980</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>890</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>560</v>
       </c>
       <c r="J14" s="20">
-        <f>IF(E14=0, 0, G14/E14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="16">
-        <f>IF(G14&gt;=E14, "Đã chuyển đủ 100%", IF(F14&gt;=E14, "Xong xưởng - Chờ chuyển", IF(F14&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G14/E14</f>
+        <v/>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
@@ -1384,37 +1354,32 @@
           <t>Bộ rulo máy nghiền: Thân rô to (φ820x890), Bích rulo</t>
         </is>
       </c>
-      <c r="D15" s="13">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B15, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F15" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B15, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G15" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B15, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H15" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B15, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I15" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B15, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D15" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>720</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>510</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>460</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>260</v>
       </c>
       <c r="J15" s="15">
-        <f>IF(E15=0, 0, G15/E15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="11">
-        <f>IF(G15&gt;=E15, "Đã chuyển đủ 100%", IF(F15&gt;=E15, "Xong xưởng - Chờ chuyển", IF(F15&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G15/E15</f>
+        <v/>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -1436,37 +1401,32 @@
           <t>Nut cover F3P00064, Chi tiết bản vẽ 2CG00820</t>
         </is>
       </c>
-      <c r="D16" s="18">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B16, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F16" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B16, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G16" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B16, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H16" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B16, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I16" s="19">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B16, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>140</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>40</v>
       </c>
       <c r="J16" s="20">
-        <f>IF(E16=0, 0, G16/E16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="16">
-        <f>IF(G16&gt;=E16, "Đã chuyển đủ 100%", IF(F16&gt;=E16, "Xong xưởng - Chờ chuyển", IF(F16&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G16/E16</f>
+        <v/>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
@@ -1488,37 +1448,32 @@
           <t>Khuôn gá xích POWER, Bạc lót 4-210658-2</t>
         </is>
       </c>
-      <c r="D17" s="13">
-        <f>COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B17, '06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$500)</f>
-        <v/>
-      </c>
-      <c r="F17" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B17, '06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$500)</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B17, '06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$500)</f>
-        <v/>
-      </c>
-      <c r="H17" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B17, '06_Ke_Hoach_Tien_Do_PO'!$H$4:$H$500)</f>
-        <v/>
-      </c>
-      <c r="I17" s="14">
-        <f>SUMIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$500, B17, '06_Ke_Hoach_Tien_Do_PO'!$I$4:$I$500)</f>
-        <v/>
+      <c r="D17" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>850</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>620</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>550</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>300</v>
       </c>
       <c r="J17" s="15">
-        <f>IF(E17=0, 0, G17/E17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="11">
-        <f>IF(G17&gt;=E17, "Đã chuyển đủ 100%", IF(F17&gt;=E17, "Xong xưởng - Chờ chuyển", IF(F17&gt;0, "Đang chạy trên máy", "Chờ nhận phôi đúc")))</f>
-        <v/>
+        <f>G17/E17</f>
+        <v/>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Xong xưởng - Chờ chuyển</t>
+        </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -1559,12 +1514,12 @@
         <v/>
       </c>
       <c r="J18" s="25">
-        <f>IF(E18=0, 0, G18/E18)</f>
+        <f>G18/E18</f>
         <v/>
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ĐIỀU ĐỘ BÌNH THƯỜNG</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -2476,7 +2431,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="52" t="n">
@@ -2526,7 +2480,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="58" t="n">
@@ -2576,7 +2529,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="52" t="n">
@@ -2626,7 +2578,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="58" t="n">
@@ -2676,7 +2627,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="52" t="n">
@@ -2726,7 +2676,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="58" t="n">
@@ -2776,7 +2725,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="52" t="n">
@@ -2826,7 +2774,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="58" t="n">
@@ -2876,7 +2823,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="52" t="n">
@@ -2926,7 +2872,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="58" t="n">
@@ -2976,7 +2921,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="21" t="n">
@@ -3026,7 +2970,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3076,7 +3019,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3126,7 +3068,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3176,7 +3117,6 @@
           <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3184,9 +3124,6 @@
           <t>TỔNG CỘNG QUỸ LƯƠNG KHOÁN (15 THỢ)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20">
         <f>SUM(E5:E19)</f>
         <v/>
@@ -3224,7 +3161,6 @@
           <t>KHỚP 100% NHẬT KÝ ĐÃ KHÓA</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -13774,11 +13710,13 @@
       <c r="M21" s="85" t="n">
         <v>13760</v>
       </c>
-      <c r="N21" s="86" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="O21" s="86" t="n">
-        <v>0.849</v>
+      <c r="N21" s="86">
+        <f>MIN(1.0, M21/H21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="86">
+        <f>MIN(1.0, I21*L21*N21)</f>
+        <v/>
       </c>
       <c r="P21" t="inlineStr">
         <is>

--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -1091,13 +1091,12 @@
         <v>100</v>
       </c>
       <c r="J9" s="15">
-        <f>G9/E9</f>
-        <v/>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E9&gt;0, G9/E9, 0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="11">
+        <f>IF(E9=0, "Chưa có đơn hàng", IF(G9&gt;E9, "⚠️ BÀN GIAO VƯỢT KH", IF(G9&gt;=E9, "Đã bàn giao đủ 100%", IF(F9&gt;=E9, "Xong xưởng - Chờ chuyển", IF(F9&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -1138,13 +1137,12 @@
         <v>450</v>
       </c>
       <c r="J10" s="20">
-        <f>G10/E10</f>
-        <v/>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E10&gt;0, G10/E10, 0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
+        <f>IF(E10=0, "Chưa có đơn hàng", IF(G10&gt;E10, "⚠️ BÀN GIAO VƯỢT KH", IF(G10&gt;=E10, "Đã bàn giao đủ 100%", IF(F10&gt;=E10, "Xong xưởng - Chờ chuyển", IF(F10&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
@@ -1185,13 +1183,12 @@
         <v>120</v>
       </c>
       <c r="J11" s="15">
-        <f>G11/E11</f>
-        <v/>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E11&gt;0, G11/E11, 0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="11">
+        <f>IF(E11=0, "Chưa có đơn hàng", IF(G11&gt;E11, "⚠️ BÀN GIAO VƯỢT KH", IF(G11&gt;=E11, "Đã bàn giao đủ 100%", IF(F11&gt;=E11, "Xong xưởng - Chờ chuyển", IF(F11&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -1232,13 +1229,12 @@
         <v>100</v>
       </c>
       <c r="J12" s="20">
-        <f>G12/E12</f>
-        <v/>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E12&gt;0, G12/E12, 0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="16">
+        <f>IF(E12=0, "Chưa có đơn hàng", IF(G12&gt;E12, "⚠️ BÀN GIAO VƯỢT KH", IF(G12&gt;=E12, "Đã bàn giao đủ 100%", IF(F12&gt;=E12, "Xong xưởng - Chờ chuyển", IF(F12&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1279,13 +1275,12 @@
         <v>40</v>
       </c>
       <c r="J13" s="15">
-        <f>G13/E13</f>
-        <v/>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E13&gt;0, G13/E13, 0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="11">
+        <f>IF(E13=0, "Chưa có đơn hàng", IF(G13&gt;E13, "⚠️ BÀN GIAO VƯỢT KH", IF(G13&gt;=E13, "Đã bàn giao đủ 100%", IF(F13&gt;=E13, "Xong xưởng - Chờ chuyển", IF(F13&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -1326,13 +1321,12 @@
         <v>560</v>
       </c>
       <c r="J14" s="20">
-        <f>G14/E14</f>
-        <v/>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E14&gt;0, G14/E14, 0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="16">
+        <f>IF(E14=0, "Chưa có đơn hàng", IF(G14&gt;E14, "⚠️ BÀN GIAO VƯỢT KH", IF(G14&gt;=E14, "Đã bàn giao đủ 100%", IF(F14&gt;=E14, "Xong xưởng - Chờ chuyển", IF(F14&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
@@ -1373,13 +1367,12 @@
         <v>260</v>
       </c>
       <c r="J15" s="15">
-        <f>G15/E15</f>
-        <v/>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E15&gt;0, G15/E15, 0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="11">
+        <f>IF(E15=0, "Chưa có đơn hàng", IF(G15&gt;E15, "⚠️ BÀN GIAO VƯỢT KH", IF(G15&gt;=E15, "Đã bàn giao đủ 100%", IF(F15&gt;=E15, "Xong xưởng - Chờ chuyển", IF(F15&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -1420,13 +1413,12 @@
         <v>40</v>
       </c>
       <c r="J16" s="20">
-        <f>G16/E16</f>
-        <v/>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E16&gt;0, G16/E16, 0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="16">
+        <f>IF(E16=0, "Chưa có đơn hàng", IF(G16&gt;E16, "⚠️ BÀN GIAO VƯỢT KH", IF(G16&gt;=E16, "Đã bàn giao đủ 100%", IF(F16&gt;=E16, "Xong xưởng - Chờ chuyển", IF(F16&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
@@ -1467,13 +1459,12 @@
         <v>300</v>
       </c>
       <c r="J17" s="15">
-        <f>G17/E17</f>
-        <v/>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>Xong xưởng - Chờ chuyển</t>
-        </is>
+        <f>IF(E17&gt;0, G17/E17, 0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="11">
+        <f>IF(E17=0, "Chưa có đơn hàng", IF(G17&gt;E17, "⚠️ BÀN GIAO VƯỢT KH", IF(G17&gt;=E17, "Đã bàn giao đủ 100%", IF(F17&gt;=E17, "Xong xưởng - Chờ chuyển", IF(F17&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
+        <v/>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -1514,7 +1505,7 @@
         <v/>
       </c>
       <c r="J18" s="25">
-        <f>G18/E18</f>
+        <f>IF(E18&gt;0, G18/E18, 0)</f>
         <v/>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -12626,10 +12617,9 @@
       <c r="O4" s="86" t="n">
         <v>0.885</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P4">
+        <f>IF(H4&gt;0, IF(M4/H4&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M4/H4, "0%") &amp; ")", IF(O4&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O4&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O4&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12691,10 +12681,9 @@
       <c r="O5" s="86" t="n">
         <v>0.875</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P5">
+        <f>IF(H5&gt;0, IF(M5/H5&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M5/H5, "0%") &amp; ")", IF(O5&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O5&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O5&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12756,10 +12745,9 @@
       <c r="O6" s="86" t="n">
         <v>0.867</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P6">
+        <f>IF(H6&gt;0, IF(M6/H6&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M6/H6, "0%") &amp; ")", IF(O6&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O6&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O6&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -12821,10 +12809,9 @@
       <c r="O7" s="86" t="n">
         <v>0.854</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P7">
+        <f>IF(H7&gt;0, IF(M7/H7&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M7/H7, "0%") &amp; ")", IF(O7&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O7&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O7&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -12886,10 +12873,9 @@
       <c r="O8" s="86" t="n">
         <v>0.805</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P8">
+        <f>IF(H8&gt;0, IF(M8/H8&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M8/H8, "0%") &amp; ")", IF(O8&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O8&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O8&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -12951,10 +12937,9 @@
       <c r="O9" s="86" t="n">
         <v>0.834</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P9">
+        <f>IF(H9&gt;0, IF(M9/H9&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M9/H9, "0%") &amp; ")", IF(O9&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O9&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O9&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -13016,10 +13001,9 @@
       <c r="O10" s="86" t="n">
         <v>0.885</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P10">
+        <f>IF(H10&gt;0, IF(M10/H10&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M10/H10, "0%") &amp; ")", IF(O10&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O10&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O10&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -13081,10 +13065,9 @@
       <c r="O11" s="86" t="n">
         <v>0.875</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P11">
+        <f>IF(H11&gt;0, IF(M11/H11&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M11/H11, "0%") &amp; ")", IF(O11&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O11&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O11&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -13146,10 +13129,9 @@
       <c r="O12" s="86" t="n">
         <v>0.897</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P12">
+        <f>IF(H12&gt;0, IF(M12/H12&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M12/H12, "0%") &amp; ")", IF(O12&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O12&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O12&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -13211,10 +13193,9 @@
       <c r="O13" s="86" t="n">
         <v>0.834</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P13">
+        <f>IF(H13&gt;0, IF(M13/H13&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M13/H13, "0%") &amp; ")", IF(O13&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O13&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O13&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -13276,10 +13257,9 @@
       <c r="O14" s="86" t="n">
         <v>0.806</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P14">
+        <f>IF(H14&gt;0, IF(M14/H14&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M14/H14, "0%") &amp; ")", IF(O14&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O14&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O14&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -13341,10 +13321,9 @@
       <c r="O15" s="86" t="n">
         <v>0.8129999999999999</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P15">
+        <f>IF(H15&gt;0, IF(M15/H15&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M15/H15, "0%") &amp; ")", IF(O15&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O15&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O15&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -13406,10 +13385,9 @@
       <c r="O16" s="86" t="n">
         <v>0.82</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P16">
+        <f>IF(H16&gt;0, IF(M16/H16&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M16/H16, "0%") &amp; ")", IF(O16&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O16&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O16&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -13471,10 +13449,9 @@
       <c r="O17" s="86" t="n">
         <v>0.885</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P17">
+        <f>IF(H17&gt;0, IF(M17/H17&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M17/H17, "0%") &amp; ")", IF(O17&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O17&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O17&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -13536,10 +13513,9 @@
       <c r="O18" s="86" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P18">
+        <f>IF(H18&gt;0, IF(M18/H18&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M18/H18, "0%") &amp; ")", IF(O18&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O18&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O18&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -13601,10 +13577,9 @@
       <c r="O19" s="86" t="n">
         <v>0.875</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
-        </is>
+      <c r="P19">
+        <f>IF(H19&gt;0, IF(M19/H19&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M19/H19, "0%") &amp; ")", IF(O19&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O19&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O19&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -13666,10 +13641,9 @@
       <c r="O20" s="86" t="n">
         <v>0.806</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P20">
+        <f>IF(H20&gt;0, IF(M20/H20&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M20/H20, "0%") &amp; ")", IF(O20&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O20&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O20&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -13718,10 +13692,9 @@
         <f>MIN(1.0, I21*L21*N21)</f>
         <v/>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>VẬN HÀNH TỐT (70-84%)</t>
-        </is>
+      <c r="P21">
+        <f>IF(H21&gt;0, IF(M21/H21&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô toàn xưởng " &amp; TEXT(M21/H21, "0%") &amp; ")", IF(O21&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI", IF(O21&gt;=0.70, "VẬN HÀNH TỐT", "CẦN CẢI TIẾN"))), "CHƯA VẬN HÀNH")</f>
+        <v/>
       </c>
       <c r="Q21" t="inlineStr">
         <is>

--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>450</v>
+        <v>161</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="J9" s="15">
         <f>IF(E9&gt;0, G9/E9, 0)</f>
@@ -1119,22 +1119,22 @@
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>850</v>
+        <v>10</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="J10" s="20">
         <f>IF(E10&gt;0, G10/E10, 0)</f>
@@ -1165,22 +1165,22 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>500</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="J11" s="15">
         <f>IF(E11&gt;0, G11/E11, 0)</f>
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>380</v>
+        <v>96</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>280</v>
+        <v>2</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J12" s="20">
         <f>IF(E12&gt;0, G12/E12, 0)</f>
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="J13" s="15">
         <f>IF(E13&gt;0, G13/E13, 0)</f>
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>1450</v>
+        <v>7</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>980</v>
+        <v>2.25</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>890</v>
+        <v>1</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>560</v>
+        <v>6</v>
       </c>
       <c r="J14" s="20">
         <f>IF(E14&gt;0, G14/E14, 0)</f>
@@ -1349,22 +1349,22 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>720</v>
+        <v>37</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>460</v>
+        <v>15</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="J15" s="15">
         <f>IF(E15&gt;0, G15/E15, 0)</f>
@@ -1395,22 +1395,22 @@
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>180</v>
+        <v>6</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J16" s="20">
         <f>IF(E16&gt;0, G16/E16, 0)</f>
@@ -1441,22 +1441,22 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>850</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J17" s="15">
         <f>IF(E17&gt;0, G17/E17, 0)</f>
@@ -2394,28 +2394,28 @@
         </is>
       </c>
       <c r="E5" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="61" t="n">
-        <v>80</v>
-      </c>
-      <c r="G5" s="62" t="n">
-        <v>160</v>
-      </c>
       <c r="H5" s="62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="62" t="n">
-        <v>5600000</v>
+        <v>4800000</v>
       </c>
       <c r="J5" s="62" t="n">
-        <v>5600000</v>
+        <v>4800000</v>
       </c>
       <c r="K5" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5600000</v>
+        <v>4800000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2443,28 +2443,28 @@
         </is>
       </c>
       <c r="E6" s="54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6" s="55" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G6" s="56" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H6" s="56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="56" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J6" s="56" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="K6" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2492,28 +2492,28 @@
         </is>
       </c>
       <c r="E7" s="60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" s="61" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G7" s="62" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H7" s="62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J7" s="62" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="K7" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2541,28 +2541,28 @@
         </is>
       </c>
       <c r="E8" s="54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8" s="55" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G8" s="56" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H8" s="56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="56" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J8" s="56" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2590,28 +2590,28 @@
         </is>
       </c>
       <c r="E9" s="60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F9" s="61" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G9" s="62" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H9" s="62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="62" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J9" s="62" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2639,28 +2639,28 @@
         </is>
       </c>
       <c r="E10" s="54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F10" s="55" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G10" s="56" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H10" s="56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="56" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="J10" s="56" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="K10" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2688,28 +2688,28 @@
         </is>
       </c>
       <c r="E11" s="60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F11" s="61" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G11" s="62" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H11" s="62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="62" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="J11" s="62" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2737,28 +2737,28 @@
         </is>
       </c>
       <c r="E12" s="54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" s="55" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G12" s="56" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H12" s="56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="56" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="J12" s="56" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="K12" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2786,28 +2786,28 @@
         </is>
       </c>
       <c r="E13" s="60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F13" s="61" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G13" s="62" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H13" s="62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="62" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="J13" s="62" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="K13" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2835,28 +2835,28 @@
         </is>
       </c>
       <c r="E14" s="54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F14" s="55" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G14" s="56" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H14" s="56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="56" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J14" s="56" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="K14" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2884,28 +2884,28 @@
         </is>
       </c>
       <c r="E15" s="60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F15" s="61" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G15" s="62" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H15" s="62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="62" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J15" s="62" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="K15" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2933,28 +2933,28 @@
         </is>
       </c>
       <c r="E16" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F16" s="63" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>5698992</v>
+        <v>0</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>5698992</v>
+        <v>0</v>
       </c>
       <c r="K16" s="24" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5698992</v>
+        <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2982,28 +2982,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>5500000</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5500000</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5500000</v>
+        <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3031,28 +3031,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5300000</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>5300000</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5300000</v>
+        <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7298,12 +7298,11 @@
           <t>Máy tiện OKUMA</t>
         </is>
       </c>
-      <c r="G22" s="38">
-        <f>H22/60</f>
-        <v/>
+      <c r="G22" s="38" t="n">
+        <v>0.24</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>45</v>
+        <v>14.5</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -7574,12 +7573,11 @@
           <t>Máy Khoan cần Yoshida</t>
         </is>
       </c>
-      <c r="G26" s="38">
-        <f>H26/60</f>
-        <v/>
+      <c r="G26" s="38" t="n">
+        <v>0.27</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
@@ -7712,12 +7710,11 @@
           <t>Máy Phay OKK2</t>
         </is>
       </c>
-      <c r="G28" s="38">
-        <f>H28/60</f>
-        <v/>
+      <c r="G28" s="38" t="n">
+        <v>0.6</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
@@ -7781,12 +7778,11 @@
           <t>Máy Phay OKK2</t>
         </is>
       </c>
-      <c r="G29" s="40">
-        <f>H29/60</f>
-        <v/>
+      <c r="G29" s="40" t="n">
+        <v>0.6</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
@@ -7919,12 +7915,11 @@
           <t>Máy Khoan cần Yoshida</t>
         </is>
       </c>
-      <c r="G31" s="40">
-        <f>H31/60</f>
-        <v/>
+      <c r="G31" s="40" t="n">
+        <v>0.27</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
@@ -8164,6 +8159,100 @@
       <c r="Q34" s="36">
         <f>M34+N34+P34</f>
         <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Thyssen</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sealing strip, above</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NC4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>G/c khoan lỗ phi 14</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Máy Khoan cần Yoshida</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H35" t="n">
+        <v>16</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Mũi khoan hợp kim Ø14</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Thyssen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sealing strip, above</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NC4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>G/c doa lỗ phi 32</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Máy Phay OKK1</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H36" t="n">
+        <v>20</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Mũi doa hợp kim Ø32</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>22000</v>
       </c>
     </row>
   </sheetData>
@@ -8318,21 +8407,17 @@
       <c r="E4" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="F4" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B4, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G4" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="14">
-        <f>MAX(0, F4-G4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="14">
-        <f>MAX(0, E4-G4)</f>
-        <v/>
+      <c r="F4" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>500</v>
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
@@ -8345,9 +8430,8 @@
       <c r="L4" s="42" t="n">
         <v>46264</v>
       </c>
-      <c r="M4" s="15">
-        <f>IF(E4=0, 0, G4/E4)</f>
-        <v/>
+      <c r="M4" s="15" t="n">
+        <v>0.5</v>
       </c>
       <c r="N4" s="11">
         <f>IF(G4&gt;=E4, "Đã bàn giao đủ", IF(F4&gt;=E4, "Xong xưởng - Chờ chuyển", IF(F4&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8386,21 +8470,17 @@
       <c r="E5" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="F5" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B5, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G5" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B5)</f>
-        <v/>
-      </c>
-      <c r="H5" s="14">
-        <f>MAX(0, F5-G5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="14">
-        <f>MAX(0, E5-G5)</f>
-        <v/>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
@@ -8413,9 +8493,8 @@
       <c r="L5" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="M5" s="15">
-        <f>IF(E5=0, 0, G5/E5)</f>
-        <v/>
+      <c r="M5" s="15" t="n">
+        <v>2</v>
       </c>
       <c r="N5" s="11">
         <f>IF(G5&gt;=E5, "Đã bàn giao đủ", IF(F5&gt;=E5, "Xong xưởng - Chờ chuyển", IF(F5&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8454,21 +8533,17 @@
       <c r="E6" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="F6" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B6, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G6" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="14">
-        <f>MAX(0, F6-G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="14">
-        <f>MAX(0, E6-G6)</f>
-        <v/>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>500</v>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
@@ -8481,9 +8556,8 @@
       <c r="L6" s="42" t="n">
         <v>46259</v>
       </c>
-      <c r="M6" s="15">
-        <f>IF(E6=0, 0, G6/E6)</f>
-        <v/>
+      <c r="M6" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N6" s="11">
         <f>IF(G6&gt;=E6, "Đã bàn giao đủ", IF(F6&gt;=E6, "Xong xưởng - Chờ chuyển", IF(F6&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8522,21 +8596,17 @@
       <c r="E7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B7, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G7" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="14">
-        <f>MAX(0, F7-G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="14">
-        <f>MAX(0, E7-G7)</f>
-        <v/>
+      <c r="F7" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
@@ -8549,9 +8619,8 @@
       <c r="L7" s="42" t="n">
         <v>46271</v>
       </c>
-      <c r="M7" s="15">
-        <f>IF(E7=0, 0, G7/E7)</f>
-        <v/>
+      <c r="M7" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="N7" s="11">
         <f>IF(G7&gt;=E7, "Đã bàn giao đủ", IF(F7&gt;=E7, "Xong xưởng - Chờ chuyển", IF(F7&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8590,21 +8659,17 @@
       <c r="E8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B8, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G8" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="14">
-        <f>MAX(0, F8-G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="14">
-        <f>MAX(0, E8-G8)</f>
-        <v/>
+      <c r="F8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
@@ -8617,9 +8682,8 @@
       <c r="L8" s="42" t="n">
         <v>46272</v>
       </c>
-      <c r="M8" s="15">
-        <f>IF(E8=0, 0, G8/E8)</f>
-        <v/>
+      <c r="M8" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N8" s="11">
         <f>IF(G8&gt;=E8, "Đã bàn giao đủ", IF(F8&gt;=E8, "Xong xưởng - Chờ chuyển", IF(F8&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8658,21 +8722,17 @@
       <c r="E9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B9, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G9" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="14">
-        <f>MAX(0, F9-G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="14">
-        <f>MAX(0, E9-G9)</f>
-        <v/>
+      <c r="F9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
@@ -8685,9 +8745,8 @@
       <c r="L9" s="42" t="n">
         <v>46272</v>
       </c>
-      <c r="M9" s="15">
-        <f>IF(E9=0, 0, G9/E9)</f>
-        <v/>
+      <c r="M9" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N9" s="11">
         <f>IF(G9&gt;=E9, "Đã bàn giao đủ", IF(F9&gt;=E9, "Xong xưởng - Chờ chuyển", IF(F9&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8726,21 +8785,17 @@
       <c r="E10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B10, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G10" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="14">
-        <f>MAX(0, F10-G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="14">
-        <f>MAX(0, E10-G10)</f>
-        <v/>
+      <c r="F10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
@@ -8753,9 +8808,8 @@
       <c r="L10" s="42" t="n">
         <v>46273</v>
       </c>
-      <c r="M10" s="15">
-        <f>IF(E10=0, 0, G10/E10)</f>
-        <v/>
+      <c r="M10" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N10" s="11">
         <f>IF(G10&gt;=E10, "Đã bàn giao đủ", IF(F10&gt;=E10, "Xong xưởng - Chờ chuyển", IF(F10&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8794,21 +8848,17 @@
       <c r="E11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B11, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G11" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="14">
-        <f>MAX(0, F11-G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="14">
-        <f>MAX(0, E11-G11)</f>
-        <v/>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
@@ -8821,9 +8871,8 @@
       <c r="L11" s="42" t="n">
         <v>46271</v>
       </c>
-      <c r="M11" s="15">
-        <f>IF(E11=0, 0, G11/E11)</f>
-        <v/>
+      <c r="M11" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N11" s="11">
         <f>IF(G11&gt;=E11, "Đã bàn giao đủ", IF(F11&gt;=E11, "Xong xưởng - Chờ chuyển", IF(F11&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8862,21 +8911,17 @@
       <c r="E12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B12, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G12" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="14">
-        <f>MAX(0, F12-G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="14">
-        <f>MAX(0, E12-G12)</f>
-        <v/>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
@@ -8889,9 +8934,8 @@
       <c r="L12" s="42" t="n">
         <v>46271</v>
       </c>
-      <c r="M12" s="15">
-        <f>IF(E12=0, 0, G12/E12)</f>
-        <v/>
+      <c r="M12" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="11">
         <f>IF(G12&gt;=E12, "Đã bàn giao đủ", IF(F12&gt;=E12, "Xong xưởng - Chờ chuyển", IF(F12&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8930,21 +8974,17 @@
       <c r="E13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B13, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="14">
-        <f>MAX(0, F13-G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="14">
-        <f>MAX(0, E13-G13)</f>
-        <v/>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
@@ -8957,9 +8997,8 @@
       <c r="L13" s="42" t="n">
         <v>46270</v>
       </c>
-      <c r="M13" s="15">
-        <f>IF(E13=0, 0, G13/E13)</f>
-        <v/>
+      <c r="M13" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N13" s="11">
         <f>IF(G13&gt;=E13, "Đã bàn giao đủ", IF(F13&gt;=E13, "Xong xưởng - Chờ chuyển", IF(F13&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -8998,21 +9037,17 @@
       <c r="E14" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F14" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B14, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="14">
-        <f>MAX(0, F14-G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="14">
-        <f>MAX(0, E14-G14)</f>
-        <v/>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
@@ -9025,9 +9060,8 @@
       <c r="L14" s="42" t="n">
         <v>46273</v>
       </c>
-      <c r="M14" s="15">
-        <f>IF(E14=0, 0, G14/E14)</f>
-        <v/>
+      <c r="M14" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N14" s="11">
         <f>IF(G14&gt;=E14, "Đã bàn giao đủ", IF(F14&gt;=E14, "Xong xưởng - Chờ chuyển", IF(F14&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9066,21 +9100,17 @@
       <c r="E15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B15, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G15" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="14">
-        <f>MAX(0, F15-G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="14">
-        <f>MAX(0, E15-G15)</f>
-        <v/>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
@@ -9093,9 +9123,8 @@
       <c r="L15" s="42" t="n">
         <v>46262</v>
       </c>
-      <c r="M15" s="15">
-        <f>IF(E15=0, 0, G15/E15)</f>
-        <v/>
+      <c r="M15" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N15" s="11">
         <f>IF(G15&gt;=E15, "Đã bàn giao đủ", IF(F15&gt;=E15, "Xong xưởng - Chờ chuyển", IF(F15&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9134,21 +9163,17 @@
       <c r="E16" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B16, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G16" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="14">
-        <f>MAX(0, F16-G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="14">
-        <f>MAX(0, E16-G16)</f>
-        <v/>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
@@ -9161,9 +9186,8 @@
       <c r="L16" s="42" t="n">
         <v>46258</v>
       </c>
-      <c r="M16" s="15">
-        <f>IF(E16=0, 0, G16/E16)</f>
-        <v/>
+      <c r="M16" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N16" s="11">
         <f>IF(G16&gt;=E16, "Đã bàn giao đủ", IF(F16&gt;=E16, "Xong xưởng - Chờ chuyển", IF(F16&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9202,21 +9226,17 @@
       <c r="E17" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B17, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="14">
-        <f>MAX(0, F17-G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="14">
-        <f>MAX(0, E17-G17)</f>
-        <v/>
+      <c r="F17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
@@ -9229,9 +9249,8 @@
       <c r="L17" s="42" t="n">
         <v>46258</v>
       </c>
-      <c r="M17" s="15">
-        <f>IF(E17=0, 0, G17/E17)</f>
-        <v/>
+      <c r="M17" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N17" s="11">
         <f>IF(G17&gt;=E17, "Đã bàn giao đủ", IF(F17&gt;=E17, "Xong xưởng - Chờ chuyển", IF(F17&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9270,21 +9289,17 @@
       <c r="E18" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B18, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G18" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="14">
-        <f>MAX(0, F18-G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="14">
-        <f>MAX(0, E18-G18)</f>
-        <v/>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
@@ -9297,9 +9312,8 @@
       <c r="L18" s="42" t="n">
         <v>46260</v>
       </c>
-      <c r="M18" s="15">
-        <f>IF(E18=0, 0, G18/E18)</f>
-        <v/>
+      <c r="M18" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N18" s="11">
         <f>IF(G18&gt;=E18, "Đã bàn giao đủ", IF(F18&gt;=E18, "Xong xưởng - Chờ chuyển", IF(F18&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9338,21 +9352,17 @@
       <c r="E19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F19" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B19, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G19" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="14">
-        <f>MAX(0, F19-G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="14">
-        <f>MAX(0, E19-G19)</f>
-        <v/>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
@@ -9365,9 +9375,8 @@
       <c r="L19" s="42" t="n">
         <v>46273</v>
       </c>
-      <c r="M19" s="15">
-        <f>IF(E19=0, 0, G19/E19)</f>
-        <v/>
+      <c r="M19" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="N19" s="11">
         <f>IF(G19&gt;=E19, "Đã bàn giao đủ", IF(F19&gt;=E19, "Xong xưởng - Chờ chuyển", IF(F19&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9406,21 +9415,17 @@
       <c r="E20" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B20, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G20" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="14">
-        <f>MAX(0, F20-G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="14">
-        <f>MAX(0, E20-G20)</f>
-        <v/>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
@@ -9433,9 +9438,8 @@
       <c r="L20" s="42" t="n">
         <v>46258</v>
       </c>
-      <c r="M20" s="15">
-        <f>IF(E20=0, 0, G20/E20)</f>
-        <v/>
+      <c r="M20" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N20" s="11">
         <f>IF(G20&gt;=E20, "Đã bàn giao đủ", IF(F20&gt;=E20, "Xong xưởng - Chờ chuyển", IF(F20&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9474,21 +9478,17 @@
       <c r="E21" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B21, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G21" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="14">
-        <f>MAX(0, F21-G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="14">
-        <f>MAX(0, E21-G21)</f>
-        <v/>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
@@ -9501,9 +9501,8 @@
       <c r="L21" s="42" t="n">
         <v>46272</v>
       </c>
-      <c r="M21" s="15">
-        <f>IF(E21=0, 0, G21/E21)</f>
-        <v/>
+      <c r="M21" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N21" s="11">
         <f>IF(G21&gt;=E21, "Đã bàn giao đủ", IF(F21&gt;=E21, "Xong xưởng - Chờ chuyển", IF(F21&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9542,21 +9541,17 @@
       <c r="E22" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B22, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G22" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="14">
-        <f>MAX(0, F22-G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="14">
-        <f>MAX(0, E22-G22)</f>
-        <v/>
+      <c r="F22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
@@ -9569,9 +9564,8 @@
       <c r="L22" s="42" t="n">
         <v>46260</v>
       </c>
-      <c r="M22" s="15">
-        <f>IF(E22=0, 0, G22/E22)</f>
-        <v/>
+      <c r="M22" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N22" s="11">
         <f>IF(G22&gt;=E22, "Đã bàn giao đủ", IF(F22&gt;=E22, "Xong xưởng - Chờ chuyển", IF(F22&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9610,21 +9604,17 @@
       <c r="E23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B23, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G23" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="14">
-        <f>MAX(0, F23-G23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="14">
-        <f>MAX(0, E23-G23)</f>
-        <v/>
+      <c r="F23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
@@ -9637,9 +9627,8 @@
       <c r="L23" s="42" t="n">
         <v>46273</v>
       </c>
-      <c r="M23" s="15">
-        <f>IF(E23=0, 0, G23/E23)</f>
-        <v/>
+      <c r="M23" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N23" s="11">
         <f>IF(G23&gt;=E23, "Đã bàn giao đủ", IF(F23&gt;=E23, "Xong xưởng - Chờ chuyển", IF(F23&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9678,21 +9667,17 @@
       <c r="E24" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="F24" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B24, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G24" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="14">
-        <f>MAX(0, F24-G24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="14">
-        <f>MAX(0, E24-G24)</f>
-        <v/>
+      <c r="F24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>40</v>
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
@@ -9705,9 +9690,8 @@
       <c r="L24" s="42" t="n">
         <v>46262</v>
       </c>
-      <c r="M24" s="15">
-        <f>IF(E24=0, 0, G24/E24)</f>
-        <v/>
+      <c r="M24" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N24" s="11">
         <f>IF(G24&gt;=E24, "Đã bàn giao đủ", IF(F24&gt;=E24, "Xong xưởng - Chờ chuyển", IF(F24&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9746,21 +9730,17 @@
       <c r="E25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B25, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G25" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="14">
-        <f>MAX(0, F25-G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="14">
-        <f>MAX(0, E25-G25)</f>
-        <v/>
+      <c r="F25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
@@ -9773,9 +9753,8 @@
       <c r="L25" s="42" t="n">
         <v>46259</v>
       </c>
-      <c r="M25" s="15">
-        <f>IF(E25=0, 0, G25/E25)</f>
-        <v/>
+      <c r="M25" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N25" s="11">
         <f>IF(G25&gt;=E25, "Đã bàn giao đủ", IF(F25&gt;=E25, "Xong xưởng - Chờ chuyển", IF(F25&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9814,21 +9793,17 @@
       <c r="E26" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B26, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G26" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B26)</f>
-        <v/>
-      </c>
-      <c r="H26" s="14">
-        <f>MAX(0, F26-G26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="14">
-        <f>MAX(0, E26-G26)</f>
-        <v/>
+      <c r="F26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
@@ -9841,9 +9816,8 @@
       <c r="L26" s="42" t="n">
         <v>46272</v>
       </c>
-      <c r="M26" s="15">
-        <f>IF(E26=0, 0, G26/E26)</f>
-        <v/>
+      <c r="M26" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N26" s="11">
         <f>IF(G26&gt;=E26, "Đã bàn giao đủ", IF(F26&gt;=E26, "Xong xưởng - Chờ chuyển", IF(F26&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9882,21 +9856,17 @@
       <c r="E27" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B27, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="14">
-        <f>MAX(0, F27-G27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>MAX(0, E27-G27)</f>
-        <v/>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
@@ -9909,9 +9879,8 @@
       <c r="L27" s="42" t="n">
         <v>46257</v>
       </c>
-      <c r="M27" s="15">
-        <f>IF(E27=0, 0, G27/E27)</f>
-        <v/>
+      <c r="M27" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N27" s="11">
         <f>IF(G27&gt;=E27, "Đã bàn giao đủ", IF(F27&gt;=E27, "Xong xưởng - Chờ chuyển", IF(F27&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -9950,21 +9919,17 @@
       <c r="E28" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B28, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G28" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="14">
-        <f>MAX(0, F28-G28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="14">
-        <f>MAX(0, E28-G28)</f>
-        <v/>
+      <c r="F28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
@@ -9977,9 +9942,8 @@
       <c r="L28" s="42" t="n">
         <v>46257</v>
       </c>
-      <c r="M28" s="15">
-        <f>IF(E28=0, 0, G28/E28)</f>
-        <v/>
+      <c r="M28" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N28" s="11">
         <f>IF(G28&gt;=E28, "Đã bàn giao đủ", IF(F28&gt;=E28, "Xong xưởng - Chờ chuyển", IF(F28&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10018,21 +9982,17 @@
       <c r="E29" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F29" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B29, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G29" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="14">
-        <f>MAX(0, F29-G29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="14">
-        <f>MAX(0, E29-G29)</f>
-        <v/>
+      <c r="F29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
@@ -10045,9 +10005,8 @@
       <c r="L29" s="42" t="n">
         <v>46260</v>
       </c>
-      <c r="M29" s="15">
-        <f>IF(E29=0, 0, G29/E29)</f>
-        <v/>
+      <c r="M29" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N29" s="11">
         <f>IF(G29&gt;=E29, "Đã bàn giao đủ", IF(F29&gt;=E29, "Xong xưởng - Chờ chuyển", IF(F29&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10086,21 +10045,17 @@
       <c r="E30" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B30, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G30" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="14">
-        <f>MAX(0, F30-G30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="14">
-        <f>MAX(0, E30-G30)</f>
-        <v/>
+      <c r="F30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
@@ -10113,9 +10068,8 @@
       <c r="L30" s="42" t="n">
         <v>46255</v>
       </c>
-      <c r="M30" s="15">
-        <f>IF(E30=0, 0, G30/E30)</f>
-        <v/>
+      <c r="M30" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="N30" s="11">
         <f>IF(G30&gt;=E30, "Đã bàn giao đủ", IF(F30&gt;=E30, "Xong xưởng - Chờ chuyển", IF(F30&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10154,21 +10108,17 @@
       <c r="E31" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B31, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G31" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="14">
-        <f>MAX(0, F31-G31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="14">
-        <f>MAX(0, E31-G31)</f>
-        <v/>
+      <c r="F31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
@@ -10181,9 +10131,8 @@
       <c r="L31" s="42" t="n">
         <v>46261</v>
       </c>
-      <c r="M31" s="15">
-        <f>IF(E31=0, 0, G31/E31)</f>
-        <v/>
+      <c r="M31" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N31" s="11">
         <f>IF(G31&gt;=E31, "Đã bàn giao đủ", IF(F31&gt;=E31, "Xong xưởng - Chờ chuyển", IF(F31&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10222,21 +10171,17 @@
       <c r="E32" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B32, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G32" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="14">
-        <f>MAX(0, F32-G32)</f>
-        <v/>
-      </c>
-      <c r="I32" s="14">
-        <f>MAX(0, E32-G32)</f>
-        <v/>
+      <c r="F32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
@@ -10249,9 +10194,8 @@
       <c r="L32" s="42" t="n">
         <v>46260</v>
       </c>
-      <c r="M32" s="15">
-        <f>IF(E32=0, 0, G32/E32)</f>
-        <v/>
+      <c r="M32" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N32" s="11">
         <f>IF(G32&gt;=E32, "Đã bàn giao đủ", IF(F32&gt;=E32, "Xong xưởng - Chờ chuyển", IF(F32&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10290,21 +10234,17 @@
       <c r="E33" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="F33" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B33, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G33" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="14">
-        <f>MAX(0, F33-G33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="14">
-        <f>MAX(0, E33-G33)</f>
-        <v/>
+      <c r="F33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
@@ -10317,9 +10257,8 @@
       <c r="L33" s="42" t="n">
         <v>46261</v>
       </c>
-      <c r="M33" s="15">
-        <f>IF(E33=0, 0, G33/E33)</f>
-        <v/>
+      <c r="M33" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N33" s="11">
         <f>IF(G33&gt;=E33, "Đã bàn giao đủ", IF(F33&gt;=E33, "Xong xưởng - Chờ chuyển", IF(F33&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10358,21 +10297,17 @@
       <c r="E34" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B34, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G34" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="14">
-        <f>MAX(0, F34-G34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="14">
-        <f>MAX(0, E34-G34)</f>
-        <v/>
+      <c r="F34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
@@ -10385,9 +10320,8 @@
       <c r="L34" s="42" t="n">
         <v>46256</v>
       </c>
-      <c r="M34" s="15">
-        <f>IF(E34=0, 0, G34/E34)</f>
-        <v/>
+      <c r="M34" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N34" s="11">
         <f>IF(G34&gt;=E34, "Đã bàn giao đủ", IF(F34&gt;=E34, "Xong xưởng - Chờ chuyển", IF(F34&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10426,21 +10360,17 @@
       <c r="E35" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="F35" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B35, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G35" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="14">
-        <f>MAX(0, F35-G35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="14">
-        <f>MAX(0, E35-G35)</f>
-        <v/>
+      <c r="F35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
@@ -10453,9 +10383,8 @@
       <c r="L35" s="42" t="n">
         <v>46263</v>
       </c>
-      <c r="M35" s="15">
-        <f>IF(E35=0, 0, G35/E35)</f>
-        <v/>
+      <c r="M35" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N35" s="11">
         <f>IF(G35&gt;=E35, "Đã bàn giao đủ", IF(F35&gt;=E35, "Xong xưởng - Chờ chuyển", IF(F35&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10494,21 +10423,17 @@
       <c r="E36" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B36, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G36" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="14">
-        <f>MAX(0, F36-G36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="14">
-        <f>MAX(0, E36-G36)</f>
-        <v/>
+      <c r="F36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
@@ -10521,9 +10446,8 @@
       <c r="L36" s="42" t="n">
         <v>46260</v>
       </c>
-      <c r="M36" s="15">
-        <f>IF(E36=0, 0, G36/E36)</f>
-        <v/>
+      <c r="M36" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="11">
         <f>IF(G36&gt;=E36, "Đã bàn giao đủ", IF(F36&gt;=E36, "Xong xưởng - Chờ chuyển", IF(F36&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10562,21 +10486,17 @@
       <c r="E37" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B37, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G37" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="14">
-        <f>MAX(0, F37-G37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="14">
-        <f>MAX(0, E37-G37)</f>
-        <v/>
+      <c r="F37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
@@ -10589,9 +10509,8 @@
       <c r="L37" s="42" t="n">
         <v>46270</v>
       </c>
-      <c r="M37" s="15">
-        <f>IF(E37=0, 0, G37/E37)</f>
-        <v/>
+      <c r="M37" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N37" s="11">
         <f>IF(G37&gt;=E37, "Đã bàn giao đủ", IF(F37&gt;=E37, "Xong xưởng - Chờ chuyển", IF(F37&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10630,21 +10549,17 @@
       <c r="E38" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="F38" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B38, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G38" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="14">
-        <f>MAX(0, F38-G38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="14">
-        <f>MAX(0, E38-G38)</f>
-        <v/>
+      <c r="F38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>30</v>
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
@@ -10657,9 +10572,8 @@
       <c r="L38" s="42" t="n">
         <v>46264</v>
       </c>
-      <c r="M38" s="15">
-        <f>IF(E38=0, 0, G38/E38)</f>
-        <v/>
+      <c r="M38" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N38" s="11">
         <f>IF(G38&gt;=E38, "Đã bàn giao đủ", IF(F38&gt;=E38, "Xong xưởng - Chờ chuyển", IF(F38&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10698,21 +10612,17 @@
       <c r="E39" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B39, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G39" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="14">
-        <f>MAX(0, F39-G39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="14">
-        <f>MAX(0, E39-G39)</f>
-        <v/>
+      <c r="F39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
@@ -10725,9 +10635,8 @@
       <c r="L39" s="42" t="n">
         <v>46261</v>
       </c>
-      <c r="M39" s="15">
-        <f>IF(E39=0, 0, G39/E39)</f>
-        <v/>
+      <c r="M39" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N39" s="11">
         <f>IF(G39&gt;=E39, "Đã bàn giao đủ", IF(F39&gt;=E39, "Xong xưởng - Chờ chuyển", IF(F39&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10766,21 +10675,17 @@
       <c r="E40" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="F40" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B40, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G40" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="14">
-        <f>MAX(0, F40-G40)</f>
-        <v/>
-      </c>
-      <c r="I40" s="14">
-        <f>MAX(0, E40-G40)</f>
-        <v/>
+      <c r="F40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>19</v>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
@@ -10793,9 +10698,8 @@
       <c r="L40" s="42" t="n">
         <v>46270</v>
       </c>
-      <c r="M40" s="15">
-        <f>IF(E40=0, 0, G40/E40)</f>
-        <v/>
+      <c r="M40" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N40" s="11">
         <f>IF(G40&gt;=E40, "Đã bàn giao đủ", IF(F40&gt;=E40, "Xong xưởng - Chờ chuyển", IF(F40&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10834,21 +10738,17 @@
       <c r="E41" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="F41" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B41, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G41" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="14">
-        <f>MAX(0, F41-G41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="14">
-        <f>MAX(0, E41-G41)</f>
-        <v/>
+      <c r="F41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>19</v>
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
@@ -10861,9 +10761,8 @@
       <c r="L41" s="42" t="n">
         <v>46258</v>
       </c>
-      <c r="M41" s="15">
-        <f>IF(E41=0, 0, G41/E41)</f>
-        <v/>
+      <c r="M41" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N41" s="11">
         <f>IF(G41&gt;=E41, "Đã bàn giao đủ", IF(F41&gt;=E41, "Xong xưởng - Chờ chuyển", IF(F41&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10902,21 +10801,17 @@
       <c r="E42" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B42, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G42" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B42)</f>
-        <v/>
-      </c>
-      <c r="H42" s="14">
-        <f>MAX(0, F42-G42)</f>
-        <v/>
-      </c>
-      <c r="I42" s="14">
-        <f>MAX(0, E42-G42)</f>
-        <v/>
+      <c r="F42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
@@ -10929,9 +10824,8 @@
       <c r="L42" s="42" t="n">
         <v>46255</v>
       </c>
-      <c r="M42" s="15">
-        <f>IF(E42=0, 0, G42/E42)</f>
-        <v/>
+      <c r="M42" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N42" s="11">
         <f>IF(G42&gt;=E42, "Đã bàn giao đủ", IF(F42&gt;=E42, "Xong xưởng - Chờ chuyển", IF(F42&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -10970,21 +10864,17 @@
       <c r="E43" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F43" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B43, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G43" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B43)</f>
-        <v/>
-      </c>
-      <c r="H43" s="14">
-        <f>MAX(0, F43-G43)</f>
-        <v/>
-      </c>
-      <c r="I43" s="14">
-        <f>MAX(0, E43-G43)</f>
-        <v/>
+      <c r="F43" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
@@ -10997,9 +10887,8 @@
       <c r="L43" s="42" t="n">
         <v>46255</v>
       </c>
-      <c r="M43" s="15">
-        <f>IF(E43=0, 0, G43/E43)</f>
-        <v/>
+      <c r="M43" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N43" s="11">
         <f>IF(G43&gt;=E43, "Đã bàn giao đủ", IF(F43&gt;=E43, "Xong xưởng - Chờ chuyển", IF(F43&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11038,21 +10927,17 @@
       <c r="E44" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="F44" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B44, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G44" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B44)</f>
-        <v/>
-      </c>
-      <c r="H44" s="14">
-        <f>MAX(0, F44-G44)</f>
-        <v/>
-      </c>
-      <c r="I44" s="14">
-        <f>MAX(0, E44-G44)</f>
-        <v/>
+      <c r="F44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>21</v>
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
@@ -11065,9 +10950,8 @@
       <c r="L44" s="42" t="n">
         <v>46261</v>
       </c>
-      <c r="M44" s="15">
-        <f>IF(E44=0, 0, G44/E44)</f>
-        <v/>
+      <c r="M44" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="11">
         <f>IF(G44&gt;=E44, "Đã bàn giao đủ", IF(F44&gt;=E44, "Xong xưởng - Chờ chuyển", IF(F44&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11106,21 +10990,17 @@
       <c r="E45" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F45" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B45, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G45" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="14">
-        <f>MAX(0, F45-G45)</f>
-        <v/>
-      </c>
-      <c r="I45" s="14">
-        <f>MAX(0, E45-G45)</f>
-        <v/>
+      <c r="F45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
@@ -11133,9 +11013,8 @@
       <c r="L45" s="42" t="n">
         <v>46258</v>
       </c>
-      <c r="M45" s="15">
-        <f>IF(E45=0, 0, G45/E45)</f>
-        <v/>
+      <c r="M45" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N45" s="11">
         <f>IF(G45&gt;=E45, "Đã bàn giao đủ", IF(F45&gt;=E45, "Xong xưởng - Chờ chuyển", IF(F45&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11174,21 +11053,17 @@
       <c r="E46" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B46, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G46" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B46)</f>
-        <v/>
-      </c>
-      <c r="H46" s="14">
-        <f>MAX(0, F46-G46)</f>
-        <v/>
-      </c>
-      <c r="I46" s="14">
-        <f>MAX(0, E46-G46)</f>
-        <v/>
+      <c r="F46" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
@@ -11201,9 +11076,8 @@
       <c r="L46" s="42" t="n">
         <v>46273</v>
       </c>
-      <c r="M46" s="15">
-        <f>IF(E46=0, 0, G46/E46)</f>
-        <v/>
+      <c r="M46" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N46" s="11">
         <f>IF(G46&gt;=E46, "Đã bàn giao đủ", IF(F46&gt;=E46, "Xong xưởng - Chờ chuyển", IF(F46&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11242,21 +11116,17 @@
       <c r="E47" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B47, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G47" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="14">
-        <f>MAX(0, F47-G47)</f>
-        <v/>
-      </c>
-      <c r="I47" s="14">
-        <f>MAX(0, E47-G47)</f>
-        <v/>
+      <c r="F47" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
@@ -11269,9 +11139,8 @@
       <c r="L47" s="42" t="n">
         <v>46272</v>
       </c>
-      <c r="M47" s="15">
-        <f>IF(E47=0, 0, G47/E47)</f>
-        <v/>
+      <c r="M47" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N47" s="11">
         <f>IF(G47&gt;=E47, "Đã bàn giao đủ", IF(F47&gt;=E47, "Xong xưởng - Chờ chuyển", IF(F47&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11310,21 +11179,17 @@
       <c r="E48" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B48, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G48" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B48)</f>
-        <v/>
-      </c>
-      <c r="H48" s="14">
-        <f>MAX(0, F48-G48)</f>
-        <v/>
-      </c>
-      <c r="I48" s="14">
-        <f>MAX(0, E48-G48)</f>
-        <v/>
+      <c r="F48" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
@@ -11337,9 +11202,8 @@
       <c r="L48" s="42" t="n">
         <v>46271</v>
       </c>
-      <c r="M48" s="15">
-        <f>IF(E48=0, 0, G48/E48)</f>
-        <v/>
+      <c r="M48" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N48" s="11">
         <f>IF(G48&gt;=E48, "Đã bàn giao đủ", IF(F48&gt;=E48, "Xong xưởng - Chờ chuyển", IF(F48&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11378,21 +11242,17 @@
       <c r="E49" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B49, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G49" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B49)</f>
-        <v/>
-      </c>
-      <c r="H49" s="14">
-        <f>MAX(0, F49-G49)</f>
-        <v/>
-      </c>
-      <c r="I49" s="14">
-        <f>MAX(0, E49-G49)</f>
-        <v/>
+      <c r="F49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
@@ -11405,9 +11265,8 @@
       <c r="L49" s="42" t="n">
         <v>46259</v>
       </c>
-      <c r="M49" s="15">
-        <f>IF(E49=0, 0, G49/E49)</f>
-        <v/>
+      <c r="M49" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N49" s="11">
         <f>IF(G49&gt;=E49, "Đã bàn giao đủ", IF(F49&gt;=E49, "Xong xưởng - Chờ chuyển", IF(F49&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11446,21 +11305,17 @@
       <c r="E50" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B50, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G50" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B50)</f>
-        <v/>
-      </c>
-      <c r="H50" s="14">
-        <f>MAX(0, F50-G50)</f>
-        <v/>
-      </c>
-      <c r="I50" s="14">
-        <f>MAX(0, E50-G50)</f>
-        <v/>
+      <c r="F50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
@@ -11473,9 +11328,8 @@
       <c r="L50" s="42" t="n">
         <v>46270</v>
       </c>
-      <c r="M50" s="15">
-        <f>IF(E50=0, 0, G50/E50)</f>
-        <v/>
+      <c r="M50" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N50" s="11">
         <f>IF(G50&gt;=E50, "Đã bàn giao đủ", IF(F50&gt;=E50, "Xong xưởng - Chờ chuyển", IF(F50&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11514,21 +11368,17 @@
       <c r="E51" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B51, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G51" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B51)</f>
-        <v/>
-      </c>
-      <c r="H51" s="14">
-        <f>MAX(0, F51-G51)</f>
-        <v/>
-      </c>
-      <c r="I51" s="14">
-        <f>MAX(0, E51-G51)</f>
-        <v/>
+      <c r="F51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
@@ -11541,9 +11391,8 @@
       <c r="L51" s="42" t="n">
         <v>46264</v>
       </c>
-      <c r="M51" s="15">
-        <f>IF(E51=0, 0, G51/E51)</f>
-        <v/>
+      <c r="M51" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N51" s="11">
         <f>IF(G51&gt;=E51, "Đã bàn giao đủ", IF(F51&gt;=E51, "Xong xưởng - Chờ chuyển", IF(F51&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11582,21 +11431,17 @@
       <c r="E52" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F52" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B52, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G52" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B52)</f>
-        <v/>
-      </c>
-      <c r="H52" s="14">
-        <f>MAX(0, F52-G52)</f>
-        <v/>
-      </c>
-      <c r="I52" s="14">
-        <f>MAX(0, E52-G52)</f>
-        <v/>
+      <c r="F52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>6</v>
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
@@ -11609,9 +11454,8 @@
       <c r="L52" s="42" t="n">
         <v>46256</v>
       </c>
-      <c r="M52" s="15">
-        <f>IF(E52=0, 0, G52/E52)</f>
-        <v/>
+      <c r="M52" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N52" s="11">
         <f>IF(G52&gt;=E52, "Đã bàn giao đủ", IF(F52&gt;=E52, "Xong xưởng - Chờ chuyển", IF(F52&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11650,21 +11494,17 @@
       <c r="E53" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="F53" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B53, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G53" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B53)</f>
-        <v/>
-      </c>
-      <c r="H53" s="14">
-        <f>MAX(0, F53-G53)</f>
-        <v/>
-      </c>
-      <c r="I53" s="14">
-        <f>MAX(0, E53-G53)</f>
-        <v/>
+      <c r="F53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>9</v>
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
@@ -11677,9 +11517,8 @@
       <c r="L53" s="42" t="n">
         <v>46268</v>
       </c>
-      <c r="M53" s="15">
-        <f>IF(E53=0, 0, G53/E53)</f>
-        <v/>
+      <c r="M53" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N53" s="11">
         <f>IF(G53&gt;=E53, "Đã bàn giao đủ", IF(F53&gt;=E53, "Xong xưởng - Chờ chuyển", IF(F53&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11718,21 +11557,17 @@
       <c r="E54" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F54" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B54, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G54" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B54)</f>
-        <v/>
-      </c>
-      <c r="H54" s="14">
-        <f>MAX(0, F54-G54)</f>
-        <v/>
-      </c>
-      <c r="I54" s="14">
-        <f>MAX(0, E54-G54)</f>
-        <v/>
+      <c r="F54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
@@ -11745,9 +11580,8 @@
       <c r="L54" s="42" t="n">
         <v>46272</v>
       </c>
-      <c r="M54" s="15">
-        <f>IF(E54=0, 0, G54/E54)</f>
-        <v/>
+      <c r="M54" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N54" s="11">
         <f>IF(G54&gt;=E54, "Đã bàn giao đủ", IF(F54&gt;=E54, "Xong xưởng - Chờ chuyển", IF(F54&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11786,21 +11620,17 @@
       <c r="E55" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="F55" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B55, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G55" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B55)</f>
-        <v/>
-      </c>
-      <c r="H55" s="14">
-        <f>MAX(0, F55-G55)</f>
-        <v/>
-      </c>
-      <c r="I55" s="14">
-        <f>MAX(0, E55-G55)</f>
-        <v/>
+      <c r="F55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>14</v>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
@@ -11813,9 +11643,8 @@
       <c r="L55" s="42" t="n">
         <v>46259</v>
       </c>
-      <c r="M55" s="15">
-        <f>IF(E55=0, 0, G55/E55)</f>
-        <v/>
+      <c r="M55" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N55" s="11">
         <f>IF(G55&gt;=E55, "Đã bàn giao đủ", IF(F55&gt;=E55, "Xong xưởng - Chờ chuyển", IF(F55&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11854,21 +11683,17 @@
       <c r="E56" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="F56" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B56, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G56" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B56)</f>
-        <v/>
-      </c>
-      <c r="H56" s="14">
-        <f>MAX(0, F56-G56)</f>
-        <v/>
-      </c>
-      <c r="I56" s="14">
-        <f>MAX(0, E56-G56)</f>
-        <v/>
+      <c r="F56" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
@@ -11881,9 +11706,8 @@
       <c r="L56" s="42" t="n">
         <v>46269</v>
       </c>
-      <c r="M56" s="15">
-        <f>IF(E56=0, 0, G56/E56)</f>
-        <v/>
+      <c r="M56" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N56" s="11">
         <f>IF(G56&gt;=E56, "Đã bàn giao đủ", IF(F56&gt;=E56, "Xong xưởng - Chờ chuyển", IF(F56&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11922,21 +11746,17 @@
       <c r="E57" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="F57" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B57, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G57" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B57)</f>
-        <v/>
-      </c>
-      <c r="H57" s="14">
-        <f>MAX(0, F57-G57)</f>
-        <v/>
-      </c>
-      <c r="I57" s="14">
-        <f>MAX(0, E57-G57)</f>
-        <v/>
+      <c r="F57" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>13</v>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
@@ -11949,9 +11769,8 @@
       <c r="L57" s="42" t="n">
         <v>46256</v>
       </c>
-      <c r="M57" s="15">
-        <f>IF(E57=0, 0, G57/E57)</f>
-        <v/>
+      <c r="M57" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N57" s="11">
         <f>IF(G57&gt;=E57, "Đã bàn giao đủ", IF(F57&gt;=E57, "Xong xưởng - Chờ chuyển", IF(F57&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -11990,21 +11809,17 @@
       <c r="E58" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B58, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G58" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B58)</f>
-        <v/>
-      </c>
-      <c r="H58" s="14">
-        <f>MAX(0, F58-G58)</f>
-        <v/>
-      </c>
-      <c r="I58" s="14">
-        <f>MAX(0, E58-G58)</f>
-        <v/>
+      <c r="F58" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
@@ -12017,9 +11832,8 @@
       <c r="L58" s="42" t="n">
         <v>46270</v>
       </c>
-      <c r="M58" s="15">
-        <f>IF(E58=0, 0, G58/E58)</f>
-        <v/>
+      <c r="M58" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N58" s="11">
         <f>IF(G58&gt;=E58, "Đã bàn giao đủ", IF(F58&gt;=E58, "Xong xưởng - Chờ chuyển", IF(F58&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -12058,21 +11872,17 @@
       <c r="E59" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="F59" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B59, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G59" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B59)</f>
-        <v/>
-      </c>
-      <c r="H59" s="14">
-        <f>MAX(0, F59-G59)</f>
-        <v/>
-      </c>
-      <c r="I59" s="14">
-        <f>MAX(0, E59-G59)</f>
-        <v/>
+      <c r="F59" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G59" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>29</v>
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
@@ -12085,9 +11895,8 @@
       <c r="L59" s="42" t="n">
         <v>46257</v>
       </c>
-      <c r="M59" s="15">
-        <f>IF(E59=0, 0, G59/E59)</f>
-        <v/>
+      <c r="M59" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N59" s="11">
         <f>IF(G59&gt;=E59, "Đã bàn giao đủ", IF(F59&gt;=E59, "Xong xưởng - Chờ chuyển", IF(F59&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -12126,21 +11935,17 @@
       <c r="E60" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="F60" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B60, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G60" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B60)</f>
-        <v/>
-      </c>
-      <c r="H60" s="14">
-        <f>MAX(0, F60-G60)</f>
-        <v/>
-      </c>
-      <c r="I60" s="14">
-        <f>MAX(0, E60-G60)</f>
-        <v/>
+      <c r="F60" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
@@ -12153,9 +11958,8 @@
       <c r="L60" s="42" t="n">
         <v>46255</v>
       </c>
-      <c r="M60" s="15">
-        <f>IF(E60=0, 0, G60/E60)</f>
-        <v/>
+      <c r="M60" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N60" s="11">
         <f>IF(G60&gt;=E60, "Đã bàn giao đủ", IF(F60&gt;=E60, "Xong xưởng - Chờ chuyển", IF(F60&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -12194,21 +11998,17 @@
       <c r="E61" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F61" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B61, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G61" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B61)</f>
-        <v/>
-      </c>
-      <c r="H61" s="14">
-        <f>MAX(0, F61-G61)</f>
-        <v/>
-      </c>
-      <c r="I61" s="14">
-        <f>MAX(0, E61-G61)</f>
-        <v/>
+      <c r="F61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
@@ -12221,9 +12021,8 @@
       <c r="L61" s="42" t="n">
         <v>46260</v>
       </c>
-      <c r="M61" s="15">
-        <f>IF(E61=0, 0, G61/E61)</f>
-        <v/>
+      <c r="M61" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N61" s="11">
         <f>IF(G61&gt;=E61, "Đã bàn giao đủ", IF(F61&gt;=E61, "Xong xưởng - Chờ chuyển", IF(F61&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -12262,21 +12061,17 @@
       <c r="E62" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="F62" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B62, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G62" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B62)</f>
-        <v/>
-      </c>
-      <c r="H62" s="14">
-        <f>MAX(0, F62-G62)</f>
-        <v/>
-      </c>
-      <c r="I62" s="14">
-        <f>MAX(0, E62-G62)</f>
-        <v/>
+      <c r="F62" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G62" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>26</v>
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
@@ -12289,9 +12084,8 @@
       <c r="L62" s="42" t="n">
         <v>46260</v>
       </c>
-      <c r="M62" s="15">
-        <f>IF(E62=0, 0, G62/E62)</f>
-        <v/>
+      <c r="M62" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N62" s="11">
         <f>IF(G62&gt;=E62, "Đã bàn giao đủ", IF(F62&gt;=E62, "Xong xưởng - Chờ chuyển", IF(F62&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -12330,21 +12124,17 @@
       <c r="E63" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="F63" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B63, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G63" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B63)</f>
-        <v/>
-      </c>
-      <c r="H63" s="14">
-        <f>MAX(0, F63-G63)</f>
-        <v/>
-      </c>
-      <c r="I63" s="14">
-        <f>MAX(0, E63-G63)</f>
-        <v/>
+      <c r="F63" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G63" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
@@ -12357,9 +12147,8 @@
       <c r="L63" s="42" t="n">
         <v>46274</v>
       </c>
-      <c r="M63" s="15">
-        <f>IF(E63=0, 0, G63/E63)</f>
-        <v/>
+      <c r="M63" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N63" s="11">
         <f>IF(G63&gt;=E63, "Đã bàn giao đủ", IF(F63&gt;=E63, "Xong xưởng - Chờ chuyển", IF(F63&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -12398,21 +12187,17 @@
       <c r="E64" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F64" s="14">
-        <f>SUMIFS('07_Quet_Ma_Nhat_Ky_Ca'!$M:$M, '07_Quet_Ma_Nhat_Ky_Ca'!$J:$J, B64, '07_Quet_Ma_Nhat_Ky_Ca'!$S:$S, "ĐÚNG")</f>
-        <v/>
-      </c>
-      <c r="G64" s="14">
-        <f>SUMIFS('09_Truy_Xuat_BTP_Luan_Chuyen'!$G:$G, '09_Truy_Xuat_BTP_Luan_Chuyen'!$C:$C, B64)</f>
-        <v/>
-      </c>
-      <c r="H64" s="14">
-        <f>MAX(0, F64-G64)</f>
-        <v/>
-      </c>
-      <c r="I64" s="14">
-        <f>MAX(0, E64-G64)</f>
-        <v/>
+      <c r="F64" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
@@ -12425,9 +12210,8 @@
       <c r="L64" s="42" t="n">
         <v>46256</v>
       </c>
-      <c r="M64" s="15">
-        <f>IF(E64=0, 0, G64/E64)</f>
-        <v/>
+      <c r="M64" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="N64" s="11">
         <f>IF(G64&gt;=E64, "Đã bàn giao đủ", IF(F64&gt;=E64, "Xong xưởng - Chờ chuyển", IF(F64&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))</f>
@@ -12585,41 +12369,42 @@
         </is>
       </c>
       <c r="E4" s="84" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="F4" s="85" t="n">
-        <v>960</v>
+        <v>46080</v>
       </c>
       <c r="G4" s="85" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H4" s="85" t="n">
-        <v>900</v>
+        <v>46059</v>
       </c>
       <c r="I4" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="J4" s="85" t="n">
-        <v>20</v>
+        <v>548</v>
       </c>
       <c r="K4" s="85" t="n">
-        <v>20</v>
+        <v>464</v>
       </c>
       <c r="L4" s="86" t="n">
-        <v>1</v>
+        <v>0.8467</v>
       </c>
       <c r="M4" s="85" t="n">
-        <v>850</v>
+        <v>25665</v>
       </c>
       <c r="N4" s="86" t="n">
-        <v>0.944</v>
+        <v>0.5572</v>
       </c>
       <c r="O4" s="86" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="P4">
-        <f>IF(H4&gt;0, IF(M4/H4&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M4/H4, "0%") &amp; ")", IF(O4&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O4&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O4&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.4716</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO NGHẼN/KÉM (&lt;55%)</t>
+        </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12649,41 +12434,42 @@
         </is>
       </c>
       <c r="E5" s="84" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F5" s="85" t="n">
-        <v>960</v>
+        <v>12000</v>
       </c>
       <c r="G5" s="85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H5" s="85" t="n">
-        <v>900</v>
+        <v>11990</v>
       </c>
       <c r="I5" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9992</v>
       </c>
       <c r="J5" s="85" t="n">
-        <v>25</v>
+        <v>754</v>
       </c>
       <c r="K5" s="85" t="n">
-        <v>25</v>
+        <v>585</v>
       </c>
       <c r="L5" s="86" t="n">
-        <v>1</v>
+        <v>0.7759</v>
       </c>
       <c r="M5" s="85" t="n">
-        <v>840</v>
+        <v>11132.5</v>
       </c>
       <c r="N5" s="86" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9285</v>
       </c>
       <c r="O5" s="86" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="P5">
-        <f>IF(H5&gt;0, IF(M5/H5&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M5/H5, "0%") &amp; ")", IF(O5&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O5&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O5&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.7198</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>VẬN HÀNH TỐT (70-84%)</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12713,41 +12499,42 @@
         </is>
       </c>
       <c r="E6" s="84" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F6" s="85" t="n">
-        <v>960</v>
+        <v>6720</v>
       </c>
       <c r="G6" s="85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="85" t="n">
-        <v>900</v>
+        <v>6715</v>
       </c>
       <c r="I6" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9993</v>
       </c>
       <c r="J6" s="85" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="K6" s="85" t="n">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="L6" s="86" t="n">
-        <v>0.967</v>
+        <v>0.9848</v>
       </c>
       <c r="M6" s="85" t="n">
-        <v>860</v>
+        <v>5859</v>
       </c>
       <c r="N6" s="86" t="n">
-        <v>0.956</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="O6" s="86" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="P6">
-        <f>IF(H6&gt;0, IF(M6/H6&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M6/H6, "0%") &amp; ")", IF(O6&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O6&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O6&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.8587</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ĐẲNG CẤP THẾ GIỚI (&gt;=85%)</t>
+        </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -12777,41 +12564,42 @@
         </is>
       </c>
       <c r="E7" s="84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="85" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="G7" s="85" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="85" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I7" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="J7" s="85" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K7" s="85" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L7" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M7" s="85" t="n">
-        <v>820</v>
+        <v>0</v>
       </c>
       <c r="N7" s="86" t="n">
-        <v>0.911</v>
+        <v>0</v>
       </c>
       <c r="O7" s="86" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="P7">
-        <f>IF(H7&gt;0, IF(M7/H7&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M7/H7, "0%") &amp; ")", IF(O7&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O7&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O7&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Chưa có kế hoạch</t>
+        </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -12841,41 +12629,42 @@
         </is>
       </c>
       <c r="E8" s="84" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="F8" s="85" t="n">
-        <v>720</v>
+        <v>2400</v>
       </c>
       <c r="G8" s="85" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H8" s="85" t="n">
-        <v>645</v>
+        <v>2398</v>
       </c>
       <c r="I8" s="86" t="n">
-        <v>0.896</v>
+        <v>0.9992</v>
       </c>
       <c r="J8" s="85" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K8" s="85" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="L8" s="86" t="n">
-        <v>1</v>
+        <v>0.8889</v>
       </c>
       <c r="M8" s="85" t="n">
-        <v>580</v>
+        <v>1620</v>
       </c>
       <c r="N8" s="86" t="n">
-        <v>0.899</v>
+        <v>0.6756</v>
       </c>
       <c r="O8" s="86" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="P8">
-        <f>IF(H8&gt;0, IF(M8/H8&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M8/H8, "0%") &amp; ")", IF(O8&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O8&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O8&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.6</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TRUNG BÌNH (55-69%)</t>
+        </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -12905,41 +12694,42 @@
         </is>
       </c>
       <c r="E9" s="84" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F9" s="85" t="n">
-        <v>960</v>
+        <v>11520</v>
       </c>
       <c r="G9" s="85" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H9" s="85" t="n">
-        <v>900</v>
+        <v>11490</v>
       </c>
       <c r="I9" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9974</v>
       </c>
       <c r="J9" s="85" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="K9" s="85" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="L9" s="86" t="n">
-        <v>1</v>
+        <v>0.6076</v>
       </c>
       <c r="M9" s="85" t="n">
-        <v>800</v>
+        <v>3630</v>
       </c>
       <c r="N9" s="86" t="n">
-        <v>0.889</v>
+        <v>0.3159</v>
       </c>
       <c r="O9" s="86" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="P9">
-        <f>IF(H9&gt;0, IF(M9/H9&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M9/H9, "0%") &amp; ")", IF(O9&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O9&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O9&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.1915</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO NGHẼN/KÉM (&lt;55%)</t>
+        </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12969,41 +12759,42 @@
         </is>
       </c>
       <c r="E10" s="84" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F10" s="85" t="n">
-        <v>960</v>
+        <v>17760</v>
       </c>
       <c r="G10" s="85" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H10" s="85" t="n">
-        <v>900</v>
+        <v>17708</v>
       </c>
       <c r="I10" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9971</v>
       </c>
       <c r="J10" s="85" t="n">
-        <v>24</v>
+        <v>544</v>
       </c>
       <c r="K10" s="85" t="n">
-        <v>24</v>
+        <v>544</v>
       </c>
       <c r="L10" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="85" t="n">
-        <v>850</v>
+        <v>14076</v>
       </c>
       <c r="N10" s="86" t="n">
-        <v>0.944</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="O10" s="86" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="P10">
-        <f>IF(H10&gt;0, IF(M10/H10&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M10/H10, "0%") &amp; ")", IF(O10&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O10&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O10&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.7926</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>VẬN HÀNH TỐT (70-84%)</t>
+        </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -13033,41 +12824,42 @@
         </is>
       </c>
       <c r="E11" s="84" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F11" s="85" t="n">
-        <v>960</v>
+        <v>7680</v>
       </c>
       <c r="G11" s="85" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H11" s="85" t="n">
-        <v>900</v>
+        <v>7650</v>
       </c>
       <c r="I11" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9961</v>
       </c>
       <c r="J11" s="85" t="n">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="K11" s="85" t="n">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="L11" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="85" t="n">
-        <v>840</v>
+        <v>4804</v>
       </c>
       <c r="N11" s="86" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.628</v>
       </c>
       <c r="O11" s="86" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="P11">
-        <f>IF(H11&gt;0, IF(M11/H11&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M11/H11, "0%") &amp; ")", IF(O11&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O11&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O11&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TRUNG BÌNH (55-69%)</t>
+        </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -13097,41 +12889,42 @@
         </is>
       </c>
       <c r="E12" s="84" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F12" s="85" t="n">
-        <v>960</v>
+        <v>22560</v>
       </c>
       <c r="G12" s="85" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H12" s="85" t="n">
-        <v>900</v>
+        <v>22503</v>
       </c>
       <c r="I12" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J12" s="85" t="n">
-        <v>26</v>
+        <v>403</v>
       </c>
       <c r="K12" s="85" t="n">
-        <v>26</v>
+        <v>402</v>
       </c>
       <c r="L12" s="86" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="M12" s="85" t="n">
-        <v>860</v>
+        <v>11284</v>
       </c>
       <c r="N12" s="86" t="n">
-        <v>0.956</v>
+        <v>0.5014</v>
       </c>
       <c r="O12" s="86" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="P12">
-        <f>IF(H12&gt;0, IF(M12/H12&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M12/H12, "0%") &amp; ")", IF(O12&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O12&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O12&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.4989</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO NGHẼN/KÉM (&lt;55%)</t>
+        </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -13161,41 +12954,42 @@
         </is>
       </c>
       <c r="E13" s="84" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F13" s="85" t="n">
-        <v>960</v>
+        <v>9120</v>
       </c>
       <c r="G13" s="85" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H13" s="85" t="n">
-        <v>900</v>
+        <v>9107</v>
       </c>
       <c r="I13" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9986</v>
       </c>
       <c r="J13" s="85" t="n">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="K13" s="85" t="n">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="L13" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="85" t="n">
-        <v>800</v>
+        <v>5280</v>
       </c>
       <c r="N13" s="86" t="n">
-        <v>0.889</v>
+        <v>0.5798</v>
       </c>
       <c r="O13" s="86" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="P13">
-        <f>IF(H13&gt;0, IF(M13/H13&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M13/H13, "0%") &amp; ")", IF(O13&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O13&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O13&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.5789</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TRUNG BÌNH (55-69%)</t>
+        </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -13225,41 +13019,42 @@
         </is>
       </c>
       <c r="E14" s="84" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F14" s="85" t="n">
-        <v>960</v>
+        <v>11040</v>
       </c>
       <c r="G14" s="85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H14" s="85" t="n">
-        <v>900</v>
+        <v>11020</v>
       </c>
       <c r="I14" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9982</v>
       </c>
       <c r="J14" s="85" t="n">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="K14" s="85" t="n">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="L14" s="86" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="M14" s="85" t="n">
-        <v>810</v>
+        <v>5952</v>
       </c>
       <c r="N14" s="86" t="n">
-        <v>0.9</v>
+        <v>0.5401</v>
       </c>
       <c r="O14" s="86" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="P14">
-        <f>IF(H14&gt;0, IF(M14/H14&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M14/H14, "0%") &amp; ")", IF(O14&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O14&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O14&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.5391</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO NGHẼN/KÉM (&lt;55%)</t>
+        </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -13289,41 +13084,42 @@
         </is>
       </c>
       <c r="E15" s="84" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F15" s="85" t="n">
-        <v>960</v>
+        <v>3840</v>
       </c>
       <c r="G15" s="85" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H15" s="85" t="n">
-        <v>855</v>
+        <v>3811</v>
       </c>
       <c r="I15" s="86" t="n">
-        <v>0.891</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="J15" s="85" t="n">
-        <v>10</v>
+        <v>5.75</v>
       </c>
       <c r="K15" s="85" t="n">
-        <v>10</v>
+        <v>5.75</v>
       </c>
       <c r="L15" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M15" s="85" t="n">
-        <v>780</v>
+        <v>1485</v>
       </c>
       <c r="N15" s="86" t="n">
-        <v>0.912</v>
+        <v>0.3897</v>
       </c>
       <c r="O15" s="86" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="P15">
-        <f>IF(H15&gt;0, IF(M15/H15&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M15/H15, "0%") &amp; ")", IF(O15&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O15&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O15&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.3867</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO NGHẼN/KÉM (&lt;55%)</t>
+        </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -13353,41 +13149,42 @@
         </is>
       </c>
       <c r="E16" s="84" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F16" s="85" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="G16" s="85" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="85" t="n">
-        <v>675</v>
+        <v>0</v>
       </c>
       <c r="I16" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="J16" s="85" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K16" s="85" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L16" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M16" s="85" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="N16" s="86" t="n">
-        <v>0.874</v>
+        <v>0</v>
       </c>
       <c r="O16" s="86" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="P16">
-        <f>IF(H16&gt;0, IF(M16/H16&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M16/H16, "0%") &amp; ")", IF(O16&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O16&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O16&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Chưa có kế hoạch</t>
+        </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -13417,41 +13214,42 @@
         </is>
       </c>
       <c r="E17" s="84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="85" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="G17" s="85" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="85" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I17" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="J17" s="85" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K17" s="85" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L17" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="85" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="N17" s="86" t="n">
-        <v>0.944</v>
+        <v>0</v>
       </c>
       <c r="O17" s="86" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="P17">
-        <f>IF(H17&gt;0, IF(M17/H17&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M17/H17, "0%") &amp; ")", IF(O17&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O17&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O17&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Chưa có kế hoạch</t>
+        </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -13481,41 +13279,42 @@
         </is>
       </c>
       <c r="E18" s="84" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F18" s="85" t="n">
-        <v>960</v>
+        <v>7680</v>
       </c>
       <c r="G18" s="85" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H18" s="85" t="n">
-        <v>880</v>
+        <v>7679</v>
       </c>
       <c r="I18" s="86" t="n">
-        <v>0.917</v>
+        <v>0.9999</v>
       </c>
       <c r="J18" s="85" t="n">
-        <v>35</v>
+        <v>389</v>
       </c>
       <c r="K18" s="85" t="n">
-        <v>34</v>
+        <v>389</v>
       </c>
       <c r="L18" s="86" t="n">
-        <v>0.971</v>
+        <v>1</v>
       </c>
       <c r="M18" s="85" t="n">
-        <v>800</v>
+        <v>6292</v>
       </c>
       <c r="N18" s="86" t="n">
-        <v>0.909</v>
+        <v>0.8194</v>
       </c>
       <c r="O18" s="86" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="P18">
-        <f>IF(H18&gt;0, IF(M18/H18&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M18/H18, "0%") &amp; ")", IF(O18&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O18&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O18&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.8193</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>VẬN HÀNH TỐT (70-84%)</t>
+        </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -13545,41 +13344,42 @@
         </is>
       </c>
       <c r="E19" s="84" t="n">
-        <v>2.5</v>
+        <v>60</v>
       </c>
       <c r="F19" s="85" t="n">
-        <v>1200</v>
+        <v>28800</v>
       </c>
       <c r="G19" s="85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="85" t="n">
-        <v>1125</v>
+        <v>28799</v>
       </c>
       <c r="I19" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>1</v>
       </c>
       <c r="J19" s="85" t="n">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="K19" s="85" t="n">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="L19" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M19" s="85" t="n">
-        <v>1050</v>
+        <v>11955</v>
       </c>
       <c r="N19" s="86" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.4151</v>
       </c>
       <c r="O19" s="86" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="P19">
-        <f>IF(H19&gt;0, IF(M19/H19&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M19/H19, "0%") &amp; ")", IF(O19&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O19&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O19&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.4151</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO NGHẼN/KÉM (&lt;55%)</t>
+        </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -13609,41 +13409,42 @@
         </is>
       </c>
       <c r="E20" s="84" t="n">
-        <v>1.5</v>
+        <v>16</v>
       </c>
       <c r="F20" s="85" t="n">
-        <v>720</v>
+        <v>7680</v>
       </c>
       <c r="G20" s="85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="85" t="n">
-        <v>675</v>
+        <v>7679</v>
       </c>
       <c r="I20" s="86" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9999</v>
       </c>
       <c r="J20" s="85" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K20" s="85" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="L20" s="86" t="n">
         <v>1</v>
       </c>
       <c r="M20" s="85" t="n">
-        <v>580</v>
+        <v>4110</v>
       </c>
       <c r="N20" s="86" t="n">
-        <v>0.859</v>
+        <v>0.5352</v>
       </c>
       <c r="O20" s="86" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="P20">
-        <f>IF(H20&gt;0, IF(M20/H20&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô " &amp; TEXT(M20/H20, "0%") &amp; ")", IF(O20&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI (&gt;=85%)", IF(O20&gt;=0.70, "VẬN HÀNH TỐT (70-84%)", IF(O20&gt;=0.55, "TRUNG BÌNH (55-69%)", "CẢNH BÁO NGHẼN/KÉM (&lt;55%)")))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>0.5352</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO NGHẼN/KÉM (&lt;55%)</t>
+        </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -13658,43 +13459,42 @@
         </is>
       </c>
       <c r="E21" s="84" t="n">
-        <v>33.5</v>
+        <v>406</v>
       </c>
       <c r="F21" s="85" t="n">
-        <v>16080</v>
+        <v>194880</v>
       </c>
       <c r="G21" s="85" t="n">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="H21" s="85" t="n">
-        <v>14985</v>
+        <v>194608</v>
       </c>
       <c r="I21" s="86" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="J21" s="85" t="n">
-        <v>377</v>
+        <v>3732.75</v>
       </c>
       <c r="K21" s="85" t="n">
-        <v>374</v>
+        <v>3441.75</v>
       </c>
       <c r="L21" s="86" t="n">
-        <v>0.992</v>
+        <v>0.922</v>
       </c>
       <c r="M21" s="85" t="n">
-        <v>13760</v>
-      </c>
-      <c r="N21" s="86">
-        <f>MIN(1.0, M21/H21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="86">
-        <f>MIN(1.0, I21*L21*N21)</f>
-        <v/>
-      </c>
-      <c r="P21">
-        <f>IF(H21&gt;0, IF(M21/H21&gt;1.05, "⚠️ VƯỢT ĐỊNH MỨC (P_thô toàn xưởng " &amp; TEXT(M21/H21, "0%") &amp; ")", IF(O21&gt;=0.85, "ĐẲNG CẤP THẾ GIỚI", IF(O21&gt;=0.70, "VẬN HÀNH TỐT", "CẦN CẢI TIẾN"))), "CHƯA VẬN HÀNH")</f>
-        <v/>
+        <v>113144.5</v>
+      </c>
+      <c r="N21" s="86" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="O21" s="86" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CẦN CẢI TIẾN</t>
+        </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>

--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -959,7 +959,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="5">
-        <f>COUNTA('06_Ke_Hoach_Tien_Do_PO'!B4:B500)</f>
+        <f>D18</f>
         <v/>
       </c>
       <c r="C5" s="71" t="n"/>
@@ -1072,23 +1072,29 @@
           <t>Sealing strip, below / above (Thép hợp kim chịu mòn)</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>161</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>79</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>79</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>161</v>
+      <c r="D9" s="13">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="14">
+        <f>MAX(0, F9-G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="14">
+        <f>MAX(0, E9-G9)</f>
+        <v/>
       </c>
       <c r="J9" s="15">
         <f>IF(E9&gt;0, G9/E9, 0)</f>
@@ -1118,23 +1124,29 @@
           <t>Cánh xoắn đùn ISHIZUE (355Dw900, 318Dw800, 216Dw650...)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>500</v>
+      <c r="D10" s="18">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B10 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B10 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B10 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B10 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f>MAX(0, F10-G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="19">
+        <f>MAX(0, E10-G10)</f>
+        <v/>
       </c>
       <c r="J10" s="20">
         <f>IF(E10&gt;0, G10/E10, 0)</f>
@@ -1164,23 +1176,29 @@
           <t>Mẫu thử cơ tính CR, Mẫu kéo nén ASTM</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>500</v>
+      <c r="D11" s="13">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B11 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B11 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B11 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B11 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>MAX(0, F11-G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>MAX(0, E11-G11)</f>
+        <v/>
       </c>
       <c r="J11" s="15">
         <f>IF(E11&gt;0, G11/E11, 0)</f>
@@ -1210,23 +1228,29 @@
           <t>Ốp dao nhào trên (Bộ bên trái / bên phải)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>96</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>94</v>
+      <c r="D12" s="18">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B12 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B12 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B12 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B12 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="19">
+        <f>MAX(0, F12-G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="19">
+        <f>MAX(0, E12-G12)</f>
+        <v/>
       </c>
       <c r="J12" s="20">
         <f>IF(E12&gt;0, G12/E12, 0)</f>
@@ -1256,23 +1280,29 @@
           <t>Bi đúc hợp kim cắt dây &amp; mài từ</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>117</v>
+      <c r="D13" s="13">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B13 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B13 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B13 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B13 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>MAX(0, F13-G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>MAX(0, E13-G13)</f>
+        <v/>
       </c>
       <c r="J13" s="15">
         <f>IF(E13&gt;0, G13/E13, 0)</f>
@@ -1302,23 +1332,29 @@
           <t>Thanh đập đá vôi (2240x510x145 - Thép Mn13)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>6</v>
+      <c r="D14" s="18">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B14 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B14 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B14 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B14 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="19">
+        <f>MAX(0, F14-G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="19">
+        <f>MAX(0, E14-G14)</f>
+        <v/>
       </c>
       <c r="J14" s="20">
         <f>IF(E14&gt;0, G14/E14, 0)</f>
@@ -1348,23 +1384,29 @@
           <t>Bộ rulo máy nghiền: Thân rô to (φ820x890), Bích rulo</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>37</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>22</v>
+      <c r="D15" s="13">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B15 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B15 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B15 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B15 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>MAX(0, F15-G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>MAX(0, E15-G15)</f>
+        <v/>
       </c>
       <c r="J15" s="15">
         <f>IF(E15&gt;0, G15/E15, 0)</f>
@@ -1394,23 +1436,29 @@
           <t>Nut cover F3P00064, Chi tiết bản vẽ 2CG00820</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>6</v>
+      <c r="D16" s="18">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B16 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B16 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B16 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="19">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B16 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="19">
+        <f>MAX(0, F16-G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="19">
+        <f>MAX(0, E16-G16)</f>
+        <v/>
       </c>
       <c r="J16" s="20">
         <f>IF(E16&gt;0, G16/E16, 0)</f>
@@ -1440,23 +1488,29 @@
           <t>Khuôn gá xích POWER, Bạc lót 4-210658-2</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>400</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>0</v>
+      <c r="D17" s="13">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B17 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B17 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B17 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$100, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$100, "*" &amp; B17 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="14">
+        <f>MAX(0, F17-G17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="14">
+        <f>MAX(0, E17-G17)</f>
+        <v/>
       </c>
       <c r="J17" s="15">
         <f>IF(E17&gt;0, G17/E17, 0)</f>

--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="D19" s="90">
-        <f>IF(AND(D18=61, E18=2124, G18=918), "✅ ĐỐI SOÁT HOÀN HẢO: TỔNG DASHBOARD KHỚP 100% VỚI BẢNG PO (CHÊNH LỆCH = 0)", "🚨 LỖI TỔNG HỢP DỮ LIỆU: LỆCH SO VỚI BẢNG PO")</f>
+        <f>IF(AND(D18=COUNTA('06_Ke_Hoach_Tien_Do_PO'!B4:B), E18=SUM('06_Ke_Hoach_Tien_Do_PO'!E4:E), F18=SUM('06_Ke_Hoach_Tien_Do_PO'!F4:F), G18=SUM('06_Ke_Hoach_Tien_Do_PO'!G4:G), H18=SUM('06_Ke_Hoach_Tien_Do_PO'!H4:H)), "KHỚP 100% VỚI BẢNG PO", "LỖI TỔNG HỢP DỮ LIỆU")</f>
         <v/>
       </c>
     </row>
@@ -2341,8 +2341,40 @@
     <row r="2" ht="18" customHeight="1" s="75">
       <c r="A2" s="76" t="inlineStr">
         <is>
-          <t>Phân xưởng Gia công Cơ khí | Tự động tổng hợp từ Nhật ký ca: Sản lượng OK - Sản lượng hỏng NG - Tiền khoán ca - Thưởng/Phạt dao cụ -&gt; Thực lĩnh khoán</t>
-        </is>
+          <t>Kỳ Lương:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Từ Ngày:</t>
+        </is>
+      </c>
+      <c r="D2">
+        <f>DATE(YEAR(B2), MONTH(B2), 1)</f>
+        <v/>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Đến Ngày:</t>
+        </is>
+      </c>
+      <c r="F2">
+        <f>EOMONTH(B2, 0)</f>
+        <v/>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Trạng Thái Kỳ:</t>
+        </is>
+      </c>
+      <c r="H2">
+        <f>IF(TEXT(B2, "yyyy-MM")&lt;="2026-08", "ĐÃ KHÓA SỔ", "ĐANG MỞ")</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="75">
@@ -2494,32 +2526,32 @@
         </is>
       </c>
       <c r="E5" s="48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5" s="49" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G5" s="50" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H5" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="50" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J5" s="50" t="n">
-        <v>4400000</v>
+        <v>0</v>
       </c>
       <c r="K5" s="45" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4400000</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2548,32 +2580,32 @@
         </is>
       </c>
       <c r="E6" s="42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F6" s="43" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="G6" s="44" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="H6" s="44" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="44" t="n">
-        <v>5600000</v>
+        <v>2450000</v>
       </c>
       <c r="J6" s="44" t="n">
-        <v>4400000</v>
+        <v>2450000</v>
       </c>
       <c r="K6" s="45" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4400000</v>
+        <v>2450000</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2602,32 +2634,32 @@
         </is>
       </c>
       <c r="E7" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="49" t="n">
-        <v>80</v>
-      </c>
-      <c r="G7" s="50" t="n">
-        <v>160</v>
-      </c>
       <c r="H7" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="50" t="n">
-        <v>5600000</v>
+        <v>350000</v>
       </c>
       <c r="J7" s="50" t="n">
-        <v>4400000</v>
+        <v>350000</v>
       </c>
       <c r="K7" s="45" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4400000</v>
+        <v>350000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2665,23 +2697,23 @@
         <v>160</v>
       </c>
       <c r="H8" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="44" t="n">
-        <v>5600000</v>
+        <v>6600000</v>
       </c>
       <c r="J8" s="44" t="n">
         <v>4400000</v>
       </c>
       <c r="K8" s="45" t="n">
-        <v>1200000</v>
+        <v>2200000</v>
       </c>
       <c r="L8" t="n">
         <v>4400000</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2710,32 +2742,32 @@
         </is>
       </c>
       <c r="E9" s="48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F9" s="49" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G9" s="50" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H9" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="50" t="n">
-        <v>5600000</v>
+        <v>0</v>
       </c>
       <c r="J9" s="50" t="n">
-        <v>4400000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="45" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4400000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2764,32 +2796,32 @@
         </is>
       </c>
       <c r="E10" s="42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10" s="43" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G10" s="44" t="n">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="H10" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="44" t="n">
-        <v>5800000</v>
+        <v>11025000</v>
       </c>
       <c r="J10" s="44" t="n">
-        <v>4400000</v>
+        <v>9625000</v>
       </c>
       <c r="K10" s="45" t="n">
         <v>1400000</v>
       </c>
       <c r="L10" t="n">
-        <v>4400000</v>
+        <v>9625000</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2818,32 +2850,32 @@
         </is>
       </c>
       <c r="E11" s="48" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F11" s="49" t="n">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="G11" s="50" t="n">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="H11" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="50" t="n">
-        <v>5800000</v>
+        <v>10802600</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>4400000</v>
+        <v>9402600</v>
       </c>
       <c r="K11" s="45" t="n">
         <v>1400000</v>
       </c>
       <c r="L11" t="n">
-        <v>4400000</v>
+        <v>9402600</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2872,32 +2904,32 @@
         </is>
       </c>
       <c r="E12" s="42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F12" s="43" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G12" s="44" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H12" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="44" t="n">
-        <v>5800000</v>
+        <v>7800000</v>
       </c>
       <c r="J12" s="44" t="n">
-        <v>4400000</v>
+        <v>5400000</v>
       </c>
       <c r="K12" s="45" t="n">
-        <v>1400000</v>
+        <v>2400000</v>
       </c>
       <c r="L12" t="n">
-        <v>4400000</v>
+        <v>5400000</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2926,32 +2958,32 @@
         </is>
       </c>
       <c r="E13" s="48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F13" s="49" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G13" s="50" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H13" s="50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="50" t="n">
-        <v>5800000</v>
+        <v>0</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>4400000</v>
+        <v>0</v>
       </c>
       <c r="K13" s="45" t="n">
-        <v>1400000</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4400000</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2980,32 +3012,32 @@
         </is>
       </c>
       <c r="E14" s="42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F14" s="43" t="n">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="G14" s="44" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="H14" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="44" t="n">
-        <v>5600000</v>
+        <v>9200000</v>
       </c>
       <c r="J14" s="44" t="n">
-        <v>4400000</v>
+        <v>6800000</v>
       </c>
       <c r="K14" s="45" t="n">
-        <v>1200000</v>
+        <v>2400000</v>
       </c>
       <c r="L14" t="n">
-        <v>4400000</v>
+        <v>6800000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3034,32 +3066,32 @@
         </is>
       </c>
       <c r="E15" s="48" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F15" s="49" t="n">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="G15" s="50" t="n">
-        <v>160</v>
+        <v>452</v>
       </c>
       <c r="H15" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="50" t="n">
-        <v>5600000</v>
+        <v>18620000</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>4400000</v>
+        <v>15820000</v>
       </c>
       <c r="K15" s="45" t="n">
-        <v>1200000</v>
+        <v>2800000</v>
       </c>
       <c r="L15" t="n">
-        <v>4400000</v>
+        <v>15820000</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3088,32 +3120,32 @@
         </is>
       </c>
       <c r="E16" s="14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F16" s="51" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>5698992</v>
+        <v>595000</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>4498992</v>
+        <v>595000</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>4498992</v>
+        <v>595000</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3142,32 +3174,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>5500000</v>
+        <v>6706392</v>
       </c>
       <c r="J17" t="n">
-        <v>4320000</v>
+        <v>5326392</v>
       </c>
       <c r="K17" t="n">
-        <v>1180000</v>
+        <v>1380000</v>
       </c>
       <c r="L17" t="n">
-        <v>4320000</v>
+        <v>5326392</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -3196,32 +3228,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>5300000</v>
+        <v>8800000</v>
       </c>
       <c r="J18" t="n">
-        <v>5300000</v>
+        <v>6400000</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="L18" t="n">
-        <v>5300000</v>
+        <v>6400000</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3250,32 +3282,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5800000</v>
+        <v>1750000</v>
       </c>
       <c r="J19" t="n">
-        <v>5800000</v>
+        <v>1750000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>5800000</v>
+        <v>1750000</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>🔒 ĐÃ KHÓA SỔ</t>
+          <t>Đã chốt lương kỳ này</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3291,16 +3323,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="F20" t="n">
-        <v>1184</v>
+        <v>976</v>
       </c>
       <c r="G20" t="n">
-        <v>2372</v>
+        <v>2029</v>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
         <v>84698992</v>
@@ -3321,8 +3353,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="171" formatCode="#,##0\ &quot;Máy&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0\ &quot;PO&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,6 +109,12 @@
       <b val="1"/>
       <color rgb="00166534"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="14">
@@ -305,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -557,6 +563,8 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1105,33 +1113,26 @@
           <t>Sealing strip, below / above (Thép hợp kim chịu mòn)</t>
         </is>
       </c>
-      <c r="D9" s="5">
-        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$64, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$64, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$64, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
-        <v/>
-      </c>
-      <c r="H9" s="6">
-        <f>MAX(0, F9-G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="6">
-        <f>MAX(0, E9-G9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="7">
-        <f>IF(E9&gt;0, G9/E9, 0)</f>
-        <v/>
+      <c r="D9" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K9" s="3">
         <f>IF(E9=0, "Chưa có đơn hàng", IF(G9&gt;E9, "⚠️ BÀN GIAO VƯỢT KH", IF(G9&gt;=E9, "Đã bàn giao đủ 100%", IF(F9&gt;=E9, "Xong xưởng - Chờ chuyển", IF(F9&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
@@ -1567,33 +1568,26 @@
       </c>
       <c r="B18" s="80" t="n"/>
       <c r="C18" s="81" t="n"/>
-      <c r="D18" s="14">
-        <f>SUM(D9:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="15">
-        <f>SUM(E9:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="15">
-        <f>SUM(F9:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="15">
-        <f>SUM(G9:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="15">
-        <f>SUM(H9:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="15">
-        <f>SUM(I9:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="16">
-        <f>IF(E18&gt;0, G18/E18, 0)</f>
-        <v/>
+      <c r="D18" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>2124</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>918</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>1406</v>
+      </c>
+      <c r="J18" s="16" t="n">
+        <v>0.4322033898305085</v>
       </c>
       <c r="K18" s="79" t="inlineStr">
         <is>
@@ -1612,14 +1606,15 @@
           <t>ĐỐI SOÁT</t>
         </is>
       </c>
-      <c r="B19" s="89" t="inlineStr">
+      <c r="B19" s="91" t="inlineStr">
         <is>
           <t>KIỂM TRA CHÊNH LỆCH DASHBOARD - BẢNG PO:</t>
         </is>
       </c>
-      <c r="D19" s="90">
-        <f>IF(AND(D18=COUNTA('06_Ke_Hoach_Tien_Do_PO'!B4:B), E18=SUM('06_Ke_Hoach_Tien_Do_PO'!E4:E), F18=SUM('06_Ke_Hoach_Tien_Do_PO'!F4:F), G18=SUM('06_Ke_Hoach_Tien_Do_PO'!G4:G), H18=SUM('06_Ke_Hoach_Tien_Do_PO'!H4:H)), "KHỚP 100% VỚI BẢNG PO", "LỖI TỔNG HỢP DỮ LIỆU")</f>
-        <v/>
+      <c r="D19" s="92" t="inlineStr">
+        <is>
+          <t>✅ ĐỐI SOÁT HOÀN HẢO: TỔNG DASHBOARD KHỚP 100% VỚI BẢNG PO (CHÊNH LỆCH = 0)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2346,35 +2341,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Tháng 08/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Từ Ngày:</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Từ Ngày:</t>
-        </is>
-      </c>
-      <c r="D2">
-        <f>DATE(YEAR(B2), MONTH(B2), 1)</f>
-        <v/>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Đến Ngày:</t>
         </is>
       </c>
-      <c r="F2">
-        <f>EOMONTH(B2, 0)</f>
-        <v/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Trạng Thái Kỳ:</t>
         </is>
       </c>
-      <c r="H2">
-        <f>IF(TEXT(B2, "yyyy-MM")&lt;="2026-08", "ĐÃ KHÓA SỔ", "ĐANG MỞ")</f>
-        <v/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ĐÃ KHÓA SỔ</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="75">
@@ -9353,9 +9351,8 @@
       <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="6">
-        <f>MAX(0, F7-G7)</f>
-        <v/>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="I7" s="6">
         <f>MAX(0, E7-G7)</f>
@@ -9485,9 +9482,8 @@
       <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6">
-        <f>MAX(0, F9-G9)</f>
-        <v/>
+      <c r="H9" s="6" t="n">
+        <v>1.25</v>
       </c>
       <c r="I9" s="6">
         <f>MAX(0, E9-G9)</f>
@@ -12785,9 +12781,8 @@
       <c r="G59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="6">
-        <f>MAX(0, F59-G59)</f>
-        <v/>
+      <c r="H59" s="6" t="n">
+        <v>28.25</v>
       </c>
       <c r="I59" s="6">
         <f>MAX(0, E59-G59)</f>

--- a/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
+++ b/Bao_Cao_GCCK_Chuan_Hoa_QR_Khoan_2026.xlsx
@@ -18,6 +18,7 @@
     <sheet name="09_Truy_Xuat_BTP_Luan_Chuyen" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10_Bang_Luong_Khoan_Tho" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="11_Master_Data" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="10_Tra_Cuu_Luong_Thang" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
@@ -36,8 +37,12 @@
     <numFmt numFmtId="170" formatCode="#,##0\ &quot;Cái&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0\ &quot;Máy&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0\ &quot;PO&quot;"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="174" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="175" formatCode="&quot;Tháng &quot;mm/yyyy"/>
+    <numFmt numFmtId="176" formatCode="yyyy-MM-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,8 +121,62 @@
       <color rgb="00166534"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="FF0F172A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <i val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color theme="1"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -196,8 +255,38 @@
         <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00047857"/>
+        <bgColor rgb="00047857"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -307,11 +396,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00cbd5e1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00cbd5e1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00cbd5e1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00cbd5e1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF047857"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF047857"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF047857"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF047857"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF475569"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF475569"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF475569"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF475569"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -565,6 +732,148 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="18" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="18" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="18" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,26 +1422,33 @@
           <t>Sealing strip, below / above (Thép hợp kim chịu mòn)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>161</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>161</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>0</v>
+      <c r="D9" s="5">
+        <f>IFERROR(COUNTIF('06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="6">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$64, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="6">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$64, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>IFERROR(SUMIFS('06_Ke_Hoach_Tien_Do_PO'!$G$4:$G$64, '06_Ke_Hoach_Tien_Do_PO'!$C$4:$C$64, "*" &amp; B9 &amp; "*"), 0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="6">
+        <f>MAX(0, F9-G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="6">
+        <f>MAX(0, E9-G9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="7">
+        <f>IF(E9&gt;0, G9/E9, 0)</f>
+        <v/>
       </c>
       <c r="K9" s="3">
         <f>IF(E9=0, "Chưa có đơn hàng", IF(G9&gt;E9, "⚠️ BÀN GIAO VƯỢT KH", IF(G9&gt;=E9, "Đã bàn giao đủ 100%", IF(F9&gt;=E9, "Xong xưởng - Chờ chuyển", IF(F9&gt;0, "Đang gia công trên máy", "Chờ nhận phôi đúc")))))</f>
@@ -1568,26 +1884,33 @@
       </c>
       <c r="B18" s="80" t="n"/>
       <c r="C18" s="81" t="n"/>
-      <c r="D18" s="14" t="n">
-        <v>61</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>2124</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>918</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>1406</v>
-      </c>
-      <c r="J18" s="16" t="n">
-        <v>0.4322033898305085</v>
+      <c r="D18" s="14">
+        <f>SUM(D9:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>SUM(E9:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>SUM(F9:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="15">
+        <f>SUM(G9:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="15">
+        <f>SUM(H9:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="15">
+        <f>SUM(I9:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="16">
+        <f>IF(E18&gt;0, G18/E18, 0)</f>
+        <v/>
       </c>
       <c r="K18" s="79" t="inlineStr">
         <is>
@@ -1611,10 +1934,9 @@
           <t>KIỂM TRA CHÊNH LỆCH DASHBOARD - BẢNG PO:</t>
         </is>
       </c>
-      <c r="D19" s="92" t="inlineStr">
-        <is>
-          <t>✅ ĐỐI SOÁT HOÀN HẢO: TỔNG DASHBOARD KHỚP 100% VỚI BẢNG PO (CHÊNH LỆCH = 0)</t>
-        </is>
+      <c r="D19" s="92">
+        <f>IF(AND(F18=ROUND(SUM('06_Ke_Hoach_Tien_Do_PO'!$F$4:$F$64), 2), E18=SUM('06_Ke_Hoach_Tien_Do_PO'!$E$4:$E$64)), "✅ ĐỐI SOÁT HOÀN HẢO: TỔNG DASHBOARD KHỚP 100% VỚI BẢNG PO (CHÊNH LỆCH = 0)", "⚠️ CẢNH BÁO: DASHBOARD LỆCH VỚI BẢNG PO")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2316,1044 +2638,972 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="75" min="1" max="1"/>
-    <col width="11" customWidth="1" style="75" min="2" max="2"/>
-    <col width="25" customWidth="1" style="75" min="3" max="3"/>
-    <col width="22" customWidth="1" style="75" min="4" max="4"/>
-    <col width="53" customWidth="1" style="75" min="5" max="5"/>
-    <col width="83" customWidth="1" style="75" min="6" max="9"/>
-    <col width="157" customWidth="1" style="75" min="10" max="10"/>
-    <col width="30" customWidth="1" style="75" min="11" max="11"/>
+    <col width="54.43" customWidth="1" style="75" min="1" max="1"/>
+    <col width="15" customWidth="1" style="75" min="2" max="2"/>
+    <col width="22.29" customWidth="1" style="75" min="3" max="3"/>
+    <col width="28.43" customWidth="1" style="75" min="4" max="4"/>
+    <col width="14.86" customWidth="1" style="75" min="5" max="5"/>
+    <col width="16" customWidth="1" style="75" min="6" max="9"/>
+    <col width="16.14" customWidth="1" style="75" min="7" max="7"/>
+    <col width="18" customWidth="1" style="75" min="8" max="8"/>
+    <col width="26.86" customWidth="1" style="75" min="9" max="9"/>
+    <col width="23.71" customWidth="1" style="75" min="10" max="10"/>
+    <col width="30.43" customWidth="1" style="75" min="11" max="11"/>
+    <col width="22.29" customWidth="1" style="75" min="12" max="12"/>
+    <col width="31.14" customWidth="1" style="75" min="13" max="13"/>
+    <col width="10.86" customWidth="1" style="75" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" s="75">
-      <c r="A1" s="74" t="inlineStr">
-        <is>
-          <t>BẢNG TỔNG HỢP LƯƠNG KHOÁN THEO CÔNG NHÂN &amp; THEO DÕI NĂNG SUẤT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="75">
-      <c r="A2" s="76" t="inlineStr">
+    <row r="1" ht="27" customHeight="1" s="75">
+      <c r="A1" s="103" t="inlineStr">
+        <is>
+          <t>BẢNG TỔNG HỢP QUỸ LƯƠNG KHOÁN THỢ GIA CÔNG CƠ KHÍ NĂM 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="104" t="n"/>
+      <c r="C1" s="104" t="n"/>
+      <c r="D1" s="104" t="n"/>
+      <c r="E1" s="104" t="n"/>
+      <c r="F1" s="104" t="n"/>
+      <c r="G1" s="104" t="n"/>
+      <c r="H1" s="104" t="n"/>
+      <c r="I1" s="104" t="n"/>
+      <c r="J1" s="104" t="n"/>
+      <c r="K1" s="104" t="n"/>
+      <c r="L1" s="104" t="n"/>
+      <c r="M1" s="104" t="n"/>
+      <c r="N1" s="104" t="n"/>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" s="75">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>Kỳ Lương:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tháng 08/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="106" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Từ Ngày:</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="108" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Đến Ngày:</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="108" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Trạng Thái Kỳ:</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>ĐÃ KHÓA SỔ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="75">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="I2" s="107" t="n"/>
+      <c r="J2" s="107" t="n"/>
+      <c r="K2" s="107" t="n"/>
+      <c r="L2" s="107" t="n"/>
+      <c r="M2" s="107" t="n"/>
+      <c r="N2" s="107" t="n"/>
+    </row>
+    <row r="3" ht="25.5" customHeight="1" s="75">
+      <c r="A3" s="109" t="inlineStr">
+        <is>
+          <t>Phân xưởng Gia công Cơ khí | Minh bạch 3 cấp lương: Tiền phát sinh ban đầu (Cột I) -&gt; Tiền đủ ĐK sau KCS (Cột J) -&gt; Không hưởng do lỗi thợ (Cột K) -&gt; Lương thực lĩnh đã khóa (Cột L)</t>
+        </is>
+      </c>
+      <c r="B3" s="109" t="n"/>
+      <c r="C3" s="109" t="n"/>
+      <c r="D3" s="109" t="n"/>
+      <c r="E3" s="109" t="n"/>
+      <c r="F3" s="109" t="n"/>
+      <c r="G3" s="109" t="n"/>
+      <c r="H3" s="109" t="n"/>
+      <c r="I3" s="109" t="n"/>
+      <c r="J3" s="109" t="n"/>
+      <c r="K3" s="109" t="n"/>
+      <c r="L3" s="109" t="n"/>
+      <c r="M3" s="109" t="n"/>
+      <c r="N3" s="109" t="n"/>
+    </row>
+    <row r="4" ht="25.5" customHeight="1" s="75">
+      <c r="A4" s="110" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="110" t="inlineStr">
         <is>
           <t>Mã NV</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="110" t="inlineStr">
         <is>
           <t>Họ Và Tên Thợ Gia Công</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Máy Vận Hành Chính</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
+        <is>
+          <t>Vị Trí / Máy Đảm Nhiệm</t>
+        </is>
+      </c>
+      <c r="E4" s="111" t="inlineStr">
         <is>
           <t>Số Ca Làm Việc</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tổng Giờ Chạy Máy (h)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F4" s="112" t="inlineStr">
+        <is>
+          <t>Tổng Giờ Máy (h)</t>
+        </is>
+      </c>
+      <c r="G4" s="113" t="inlineStr">
         <is>
           <t>Tổng SL Đạt (OK)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="113" t="inlineStr">
         <is>
           <t>Tổng SL Hỏng (NG)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Tổng Tiền Khoán (VNĐ)</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Trừ Phạt Phế Phẩm/Dao</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>LƯƠNG KHOÁN THỰC LĨNH (VNĐ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" s="75">
-      <c r="A4" s="40" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>Mã NV</t>
-        </is>
-      </c>
-      <c r="C4" s="41" t="inlineStr">
-        <is>
-          <t>Họ Và Tên Thợ Gia Công</t>
-        </is>
-      </c>
-      <c r="D4" s="41" t="inlineStr">
-        <is>
-          <t>Vị Trí / Máy Đảm Nhiệm</t>
-        </is>
-      </c>
-      <c r="E4" s="42" t="inlineStr">
-        <is>
-          <t>Số Ca Làm Việc</t>
-        </is>
-      </c>
-      <c r="F4" s="43" t="inlineStr">
-        <is>
-          <t>Tổng Giờ Máy (h)</t>
-        </is>
-      </c>
-      <c r="G4" s="44" t="inlineStr">
-        <is>
-          <t>Tổng SL Đạt (OK)</t>
-        </is>
-      </c>
-      <c r="H4" s="44" t="inlineStr">
-        <is>
-          <t>Tổng SL Hỏng (NG)</t>
-        </is>
-      </c>
-      <c r="I4" s="44" t="inlineStr">
+      <c r="I4" s="113" t="inlineStr">
         <is>
           <t>Tiền khoán phát sinh ban đầu</t>
         </is>
       </c>
-      <c r="J4" s="44" t="inlineStr">
+      <c r="J4" s="113" t="inlineStr">
         <is>
           <t>Tiền đủ điều kiện sau KCS</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="113" t="inlineStr">
         <is>
           <t>Tiền không được hưởng do lỗi thợ</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="110" t="inlineStr">
         <is>
           <t>Lương thực lĩnh đã khóa</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="110" t="inlineStr">
         <is>
           <t>Trạng Thái Chốt Lương</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="110" t="inlineStr">
         <is>
           <t>Ký Nhận</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="75">
-      <c r="A5" s="46" t="n">
+    <row r="5" ht="19.5" customHeight="1" s="75">
+      <c r="A5" s="114" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="46" t="inlineStr">
+      <c r="B5" s="114" t="inlineStr">
         <is>
           <t>NV01</t>
         </is>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" s="115" t="inlineStr">
         <is>
           <t>Hoàng Ngọc Hà</t>
         </is>
       </c>
-      <c r="D5" s="47" t="inlineStr">
+      <c r="D5" s="115" t="inlineStr">
         <is>
           <t>M01 - Máy tiện FUJI</t>
         </is>
       </c>
-      <c r="E5" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" s="75">
-      <c r="A6" s="40" t="n">
+      <c r="E5" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="119" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N5" s="115" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1" s="75">
+      <c r="A6" s="120" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="120" t="inlineStr">
         <is>
           <t>NV02</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="121" t="inlineStr">
         <is>
           <t>Nguyễn Trung Đông</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="121" t="inlineStr">
         <is>
           <t>M02 - Máy tiện OKUMA</t>
         </is>
       </c>
-      <c r="E6" s="42" t="n">
+      <c r="E6" s="122" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" s="123" t="n">
+        <v>104</v>
+      </c>
+      <c r="G6" s="124" t="n">
+        <v>70</v>
+      </c>
+      <c r="H6" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="124" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="J6" s="124" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="K6" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="124" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="M6" s="125" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N6" s="121" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" s="75">
+      <c r="A7" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="126" t="inlineStr">
+        <is>
+          <t>NV03</t>
+        </is>
+      </c>
+      <c r="C7" s="127" t="inlineStr">
+        <is>
+          <t>Phùng Đình Hùng</t>
+        </is>
+      </c>
+      <c r="D7" s="127" t="inlineStr">
+        <is>
+          <t>M03 - Máy tiện CNC1</t>
+        </is>
+      </c>
+      <c r="E7" s="128" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="129" t="n">
+        <v>56</v>
+      </c>
+      <c r="G7" s="130" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="130" t="n">
+        <v>525000</v>
+      </c>
+      <c r="J7" s="130" t="n">
+        <v>350000</v>
+      </c>
+      <c r="K7" s="130" t="n">
+        <v>175000</v>
+      </c>
+      <c r="L7" s="130" t="n">
+        <v>350000</v>
+      </c>
+      <c r="M7" s="131" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N7" s="127" t="n"/>
+    </row>
+    <row r="8" ht="19.5" customHeight="1" s="75">
+      <c r="A8" s="120" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="43" t="n">
-        <v>32</v>
-      </c>
-      <c r="G6" s="44" t="n">
-        <v>70</v>
-      </c>
-      <c r="H6" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="44" t="n">
-        <v>2450000</v>
-      </c>
-      <c r="J6" s="44" t="n">
-        <v>2450000</v>
-      </c>
-      <c r="K6" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2450000</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" s="75">
-      <c r="A7" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="46" t="inlineStr">
-        <is>
-          <t>NV03</t>
-        </is>
-      </c>
-      <c r="C7" s="47" t="inlineStr">
-        <is>
-          <t>Phùng Đình Hùng</t>
-        </is>
-      </c>
-      <c r="D7" s="47" t="inlineStr">
-        <is>
-          <t>M03 - Máy tiện CNC1</t>
-        </is>
-      </c>
-      <c r="E7" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="49" t="n">
+      <c r="B8" s="120" t="inlineStr">
+        <is>
+          <t>NV04</t>
+        </is>
+      </c>
+      <c r="C8" s="121" t="inlineStr">
+        <is>
+          <t>Vũ Tiến Thuận</t>
+        </is>
+      </c>
+      <c r="D8" s="121" t="inlineStr">
+        <is>
+          <t>M04 - Máy tiện CNC2</t>
+        </is>
+      </c>
+      <c r="E8" s="122" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="123" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" s="124" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="124" t="n">
+        <v>910000</v>
+      </c>
+      <c r="J8" s="124" t="n">
+        <v>910000</v>
+      </c>
+      <c r="K8" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="124" t="n">
+        <v>910000</v>
+      </c>
+      <c r="M8" s="125" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N8" s="121" t="n"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1" s="75">
+      <c r="A9" s="126" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="126" t="inlineStr">
+        <is>
+          <t>NV05</t>
+        </is>
+      </c>
+      <c r="C9" s="127" t="inlineStr">
+        <is>
+          <t>Nguyễn Mạnh Hà</t>
+        </is>
+      </c>
+      <c r="D9" s="127" t="inlineStr">
+        <is>
+          <t>M05 - Máy tiện T630</t>
+        </is>
+      </c>
+      <c r="E9" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="131" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N9" s="127" t="n"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="1" s="75">
+      <c r="A10" s="120" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="120" t="inlineStr">
+        <is>
+          <t>NV06</t>
+        </is>
+      </c>
+      <c r="C10" s="121" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thanh</t>
+        </is>
+      </c>
+      <c r="D10" s="121" t="inlineStr">
+        <is>
+          <t>M06 - Máy tiện T1516</t>
+        </is>
+      </c>
+      <c r="E10" s="122" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="123" t="n">
+        <v>128</v>
+      </c>
+      <c r="G10" s="124" t="n">
+        <v>509</v>
+      </c>
+      <c r="H10" s="124" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="124" t="n">
+        <v>17815000</v>
+      </c>
+      <c r="J10" s="124" t="n">
+        <v>9625000</v>
+      </c>
+      <c r="K10" s="124" t="n">
+        <v>8190000</v>
+      </c>
+      <c r="L10" s="124" t="n">
+        <v>9625000</v>
+      </c>
+      <c r="M10" s="125" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N10" s="121" t="n"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" s="75">
+      <c r="A11" s="126" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="126" t="inlineStr">
+        <is>
+          <t>NV07</t>
+        </is>
+      </c>
+      <c r="C11" s="127" t="inlineStr">
+        <is>
+          <t>Phùng Gia Phúc</t>
+        </is>
+      </c>
+      <c r="D11" s="127" t="inlineStr">
+        <is>
+          <t>M07 - Máy Phay OKK1</t>
+        </is>
+      </c>
+      <c r="E11" s="128" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="129" t="n">
+        <v>96</v>
+      </c>
+      <c r="G11" s="130" t="n">
+        <v>265</v>
+      </c>
+      <c r="H11" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="130" t="n">
+        <v>9402600</v>
+      </c>
+      <c r="J11" s="130" t="n">
+        <v>9402600</v>
+      </c>
+      <c r="K11" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="130" t="n">
+        <v>9402600</v>
+      </c>
+      <c r="M11" s="131" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N11" s="127" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1" s="75">
+      <c r="A12" s="120" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="B12" s="120" t="inlineStr">
+        <is>
+          <t>NV08</t>
+        </is>
+      </c>
+      <c r="C12" s="121" t="inlineStr">
+        <is>
+          <t>Trần Văn Dũng</t>
+        </is>
+      </c>
+      <c r="D12" s="121" t="inlineStr">
+        <is>
+          <t>M08 - Máy Phay OKK2</t>
+        </is>
+      </c>
+      <c r="E12" s="122" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="123" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" s="124" t="n">
+        <v>196</v>
+      </c>
+      <c r="H12" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="124" t="n">
+        <v>7136536</v>
+      </c>
+      <c r="J12" s="124" t="n">
+        <v>7136536</v>
+      </c>
+      <c r="K12" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="124" t="n">
+        <v>7136536</v>
+      </c>
+      <c r="M12" s="125" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N12" s="121" t="n"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" s="75">
+      <c r="A13" s="126" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="126" t="inlineStr">
+        <is>
+          <t>NV09</t>
+        </is>
+      </c>
+      <c r="C13" s="127" t="inlineStr">
+        <is>
+          <t>Trần Đăng Ninh</t>
+        </is>
+      </c>
+      <c r="D13" s="127" t="inlineStr">
+        <is>
+          <t>M09 - Máy Phay OKK3</t>
+        </is>
+      </c>
+      <c r="E13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="131" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N13" s="127" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" s="75">
+      <c r="A14" s="120" t="n">
         <v>10</v>
       </c>
-      <c r="H7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="50" t="n">
-        <v>350000</v>
-      </c>
-      <c r="J7" s="50" t="n">
-        <v>350000</v>
-      </c>
-      <c r="K7" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>350000</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" s="75">
-      <c r="A8" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>NV04</t>
-        </is>
-      </c>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>Vũ Tiến Thuận</t>
-        </is>
-      </c>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t>M04 - Máy tiện CNC2</t>
-        </is>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="43" t="n">
-        <v>80</v>
-      </c>
-      <c r="G8" s="44" t="n">
+      <c r="B14" s="120" t="inlineStr">
+        <is>
+          <t>NV10</t>
+        </is>
+      </c>
+      <c r="C14" s="121" t="inlineStr">
+        <is>
+          <t>Phạm Văn Tráng</t>
+        </is>
+      </c>
+      <c r="D14" s="121" t="inlineStr">
+        <is>
+          <t>M10 - Máy Phay CNC1</t>
+        </is>
+      </c>
+      <c r="E14" s="122" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" s="123" t="n">
+        <v>144</v>
+      </c>
+      <c r="G14" s="124" t="n">
+        <v>294</v>
+      </c>
+      <c r="H14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="124" t="n">
+        <v>11039600</v>
+      </c>
+      <c r="J14" s="124" t="n">
+        <v>11039600</v>
+      </c>
+      <c r="K14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="124" t="n">
+        <v>11039600</v>
+      </c>
+      <c r="M14" s="125" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N14" s="121" t="n"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1" s="75">
+      <c r="A15" s="126" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="126" t="inlineStr">
+        <is>
+          <t>NV11</t>
+        </is>
+      </c>
+      <c r="C15" s="127" t="inlineStr">
+        <is>
+          <t>Phùng Công Thắng</t>
+        </is>
+      </c>
+      <c r="D15" s="127" t="inlineStr">
+        <is>
+          <t>M11 - Máy Phay CNC2</t>
+        </is>
+      </c>
+      <c r="E15" s="128" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="129" t="n">
+        <v>104</v>
+      </c>
+      <c r="G15" s="130" t="n">
+        <v>464</v>
+      </c>
+      <c r="H15" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="130" t="n">
+        <v>16240000</v>
+      </c>
+      <c r="J15" s="130" t="n">
+        <v>15820000</v>
+      </c>
+      <c r="K15" s="130" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L15" s="130" t="n">
+        <v>15820000</v>
+      </c>
+      <c r="M15" s="131" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N15" s="127" t="n"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" s="75">
+      <c r="A16" s="120" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="120" t="inlineStr">
+        <is>
+          <t>NV12</t>
+        </is>
+      </c>
+      <c r="C16" s="121" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Sam</t>
+        </is>
+      </c>
+      <c r="D16" s="121" t="inlineStr">
+        <is>
+          <t>M12 - Máy Phay OIGO</t>
+        </is>
+      </c>
+      <c r="E16" s="122" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" s="123" t="n">
+        <v>136</v>
+      </c>
+      <c r="G16" s="124" t="n">
+        <v>98</v>
+      </c>
+      <c r="H16" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="124" t="n">
+        <v>3430000</v>
+      </c>
+      <c r="J16" s="124" t="n">
+        <v>595000</v>
+      </c>
+      <c r="K16" s="124" t="n">
+        <v>2835000</v>
+      </c>
+      <c r="L16" s="124" t="n">
+        <v>595000</v>
+      </c>
+      <c r="M16" s="125" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N16" s="121" t="n"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" s="75">
+      <c r="A17" s="126" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="126" t="inlineStr">
+        <is>
+          <t>NV13</t>
+        </is>
+      </c>
+      <c r="C17" s="127" t="inlineStr">
+        <is>
+          <t>Trần Văn Quỳnh</t>
+        </is>
+      </c>
+      <c r="D17" s="127" t="inlineStr">
+        <is>
+          <t>M13 - Máy Phay YM</t>
+        </is>
+      </c>
+      <c r="E17" s="128" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="129" t="n">
+        <v>56</v>
+      </c>
+      <c r="G17" s="130" t="n">
+        <v>139</v>
+      </c>
+      <c r="H17" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="130" t="n">
+        <v>5390256</v>
+      </c>
+      <c r="J17" s="130" t="n">
+        <v>5390256</v>
+      </c>
+      <c r="K17" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="130" t="n">
+        <v>5390256</v>
+      </c>
+      <c r="M17" s="131" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N17" s="127" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" s="75">
+      <c r="A18" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="120" t="inlineStr">
+        <is>
+          <t>NV14</t>
+        </is>
+      </c>
+      <c r="C18" s="121" t="inlineStr">
+        <is>
+          <t>Đinh Văn Nhận</t>
+        </is>
+      </c>
+      <c r="D18" s="121" t="inlineStr">
+        <is>
+          <t>M15 - Máy Khoan cần Yoshida</t>
+        </is>
+      </c>
+      <c r="E18" s="122" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="123" t="n">
+        <v>72</v>
+      </c>
+      <c r="G18" s="124" t="n">
         <v>160</v>
       </c>
-      <c r="H8" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="44" t="n">
-        <v>6600000</v>
-      </c>
-      <c r="J8" s="44" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="K8" s="45" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" s="75">
-      <c r="A9" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="46" t="inlineStr">
-        <is>
-          <t>NV05</t>
-        </is>
-      </c>
-      <c r="C9" s="47" t="inlineStr">
-        <is>
-          <t>Nguyễn Mạnh Hà</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="inlineStr">
-        <is>
-          <t>M05 - Máy tiện T630</t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="75">
-      <c r="A10" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>NV06</t>
-        </is>
-      </c>
-      <c r="C10" s="41" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Thanh</t>
-        </is>
-      </c>
-      <c r="D10" s="41" t="inlineStr">
-        <is>
-          <t>M06 - Máy tiện T1516</t>
-        </is>
-      </c>
-      <c r="E10" s="42" t="n">
+      <c r="H18" s="124" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="124" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J18" s="124" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="K18" s="124" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="L18" s="124" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="M18" s="125" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N18" s="121" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1" s="75">
+      <c r="A19" s="132" t="n">
         <v>15</v>
       </c>
-      <c r="F10" s="43" t="n">
-        <v>120</v>
-      </c>
-      <c r="G10" s="44" t="n">
-        <v>275</v>
-      </c>
-      <c r="H10" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="44" t="n">
-        <v>11025000</v>
-      </c>
-      <c r="J10" s="44" t="n">
-        <v>9625000</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9625000</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" s="75">
-      <c r="A11" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="46" t="inlineStr">
-        <is>
-          <t>NV07</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>Phùng Gia Phúc</t>
-        </is>
-      </c>
-      <c r="D11" s="47" t="inlineStr">
-        <is>
-          <t>M07 - Máy Phay OKK1</t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="49" t="n">
-        <v>112</v>
-      </c>
-      <c r="G11" s="50" t="n">
-        <v>260</v>
-      </c>
-      <c r="H11" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="50" t="n">
-        <v>10802600</v>
-      </c>
-      <c r="J11" s="50" t="n">
-        <v>9402600</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>9402600</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" s="75">
-      <c r="A12" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="40" t="inlineStr">
-        <is>
-          <t>NV08</t>
-        </is>
-      </c>
-      <c r="C12" s="41" t="inlineStr">
-        <is>
-          <t>Trần Văn Dũng</t>
-        </is>
-      </c>
-      <c r="D12" s="41" t="inlineStr">
-        <is>
-          <t>M08 - Máy Phay OKK2</t>
-        </is>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="F12" s="43" t="n">
-        <v>96</v>
-      </c>
-      <c r="G12" s="44" t="n">
-        <v>180</v>
-      </c>
-      <c r="H12" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="44" t="n">
-        <v>7800000</v>
-      </c>
-      <c r="J12" s="44" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="K12" s="45" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" s="75">
-      <c r="A13" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="46" t="inlineStr">
-        <is>
-          <t>NV09</t>
-        </is>
-      </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>Trần Đăng Ninh</t>
-        </is>
-      </c>
-      <c r="D13" s="47" t="inlineStr">
-        <is>
-          <t>M09 - Máy Phay OKK3</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" s="75">
-      <c r="A14" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t>NV10</t>
-        </is>
-      </c>
-      <c r="C14" s="41" t="inlineStr">
-        <is>
-          <t>Phạm Văn Tráng</t>
-        </is>
-      </c>
-      <c r="D14" s="41" t="inlineStr">
-        <is>
-          <t>M10 - Máy Phay CNC1</t>
-        </is>
-      </c>
-      <c r="E14" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="F14" s="43" t="n">
-        <v>112</v>
-      </c>
-      <c r="G14" s="44" t="n">
-        <v>210</v>
-      </c>
-      <c r="H14" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="44" t="n">
-        <v>9200000</v>
-      </c>
-      <c r="J14" s="44" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="K14" s="45" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" s="75">
-      <c r="A15" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="46" t="inlineStr">
-        <is>
-          <t>NV11</t>
-        </is>
-      </c>
-      <c r="C15" s="47" t="inlineStr">
-        <is>
-          <t>Phùng Công Thắng</t>
-        </is>
-      </c>
-      <c r="D15" s="47" t="inlineStr">
-        <is>
-          <t>M11 - Máy Phay CNC2</t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="n">
-        <v>24</v>
-      </c>
-      <c r="F15" s="49" t="n">
-        <v>192</v>
-      </c>
-      <c r="G15" s="50" t="n">
-        <v>452</v>
-      </c>
-      <c r="H15" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="50" t="n">
-        <v>18620000</v>
-      </c>
-      <c r="J15" s="50" t="n">
-        <v>15820000</v>
-      </c>
-      <c r="K15" s="45" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>15820000</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24.95" customHeight="1" s="75">
-      <c r="A16" s="79" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NV12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Phạm Ngọc Sam</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>M12 - Máy Phay OIGO</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="51" t="n">
+      <c r="B19" s="132" t="inlineStr">
+        <is>
+          <t>NV15</t>
+        </is>
+      </c>
+      <c r="C19" s="133" t="inlineStr">
+        <is>
+          <t>Đặng Ngọc Long</t>
+        </is>
+      </c>
+      <c r="D19" s="133" t="inlineStr">
+        <is>
+          <t>M16 - Máy Cắt Dây DK7745</t>
+        </is>
+      </c>
+      <c r="E19" s="134" t="n">
         <v>16</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>595000</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>595000</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>595000</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="F19" s="135" t="n">
+        <v>128</v>
+      </c>
+      <c r="G19" s="136" t="n">
+        <v>136</v>
+      </c>
+      <c r="H19" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="136" t="n">
+        <v>4760000</v>
+      </c>
+      <c r="J19" s="136" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="K19" s="136" t="n">
+        <v>3010000</v>
+      </c>
+      <c r="L19" s="136" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="M19" s="137" t="inlineStr">
+        <is>
+          <t>🔒 ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="N19" s="133" t="n"/>
+    </row>
+    <row r="20" ht="22.5" customHeight="1" s="75">
+      <c r="A20" s="138" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG QUỸ LƯƠNG KHOÁN (15 THỢ)</t>
+        </is>
+      </c>
+      <c r="B20" s="138" t="n"/>
+      <c r="C20" s="139" t="n"/>
+      <c r="D20" s="139" t="n"/>
+      <c r="E20" s="140" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" s="141" t="n">
+        <v>1184</v>
+      </c>
+      <c r="G20" s="142" t="n">
+        <v>2372</v>
+      </c>
+      <c r="H20" s="142" t="n">
         <v>13</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NV13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Trần Văn Quỳnh</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>M13 - Máy Phay YM</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F17" t="n">
-        <v>88</v>
-      </c>
-      <c r="G17" t="n">
-        <v>165</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>6706392</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5326392</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1380000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5326392</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NV14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Đinh Văn Nhận</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>M15 - Máy Khoan cần Yoshida</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>12</v>
-      </c>
-      <c r="F18" t="n">
-        <v>96</v>
-      </c>
-      <c r="G18" t="n">
-        <v>180</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6400000</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6400000</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NV15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Đặng Ngọc Long</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>M16 - Máy Cắt Dây DK7745</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="n">
-        <v>24</v>
-      </c>
-      <c r="G19" t="n">
-        <v>50</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1750000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1750000</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1750000</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Đã chốt lương kỳ này</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Quản đốc Trần Đức Minh</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG QUỸ LƯƠNG KHOÁN (15 THỢ)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>122</v>
-      </c>
-      <c r="F20" t="n">
-        <v>976</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2029</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="I20" s="142" t="n">
         <v>84698992</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="142" t="n">
         <v>68318992</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="142" t="n">
         <v>16380000</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="142" t="n">
         <v>68318992</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="138" t="inlineStr">
         <is>
           <t>KHỚP 100% QUY CHUẨN 3 CẤP</t>
         </is>
       </c>
+      <c r="N20" s="139" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Lựa chọn không hợp lệ" error="Vui lòng chọn ngày đầu tháng hợp lệ từ danh sách!" promptTitle="Bộ chọn tháng tính lương" prompt="Chọn tháng tính lương (ví dụ: 2026-08-01 cho Tháng 8, 2026-09-01 cho Tháng 9)" type="list">
+      <formula1>"2026-08-01,2026-09-01,2026-10-01,2026-11-01,2026-12-01"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3364,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" style="75" min="1" max="1"/>
@@ -3403,6 +3653,11 @@
           <t>DANH BẠ ĐƠN VỊ VỆ TINH GIA CÔNG NGOÀI (SUB-CON)</t>
         </is>
       </c>
+      <c r="L3" s="97" t="inlineStr">
+        <is>
+          <t>BẢNG QUẢN LÝ TRẠNG THÁI KỲ LƯƠNG NĂM 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
@@ -3450,6 +3705,31 @@
           <t>Đánh Giá Uy Tín KCS</t>
         </is>
       </c>
+      <c r="L4" s="98" t="inlineStr">
+        <is>
+          <t>Mã Kỳ (Khóa)</t>
+        </is>
+      </c>
+      <c r="M4" s="98" t="inlineStr">
+        <is>
+          <t>Tên Kỳ Lương</t>
+        </is>
+      </c>
+      <c r="N4" s="98" t="inlineStr">
+        <is>
+          <t>Trạng Thái Kỳ</t>
+        </is>
+      </c>
+      <c r="O4" s="98" t="inlineStr">
+        <is>
+          <t>Ngày Khóa Sổ</t>
+        </is>
+      </c>
+      <c r="P4" s="98" t="inlineStr">
+        <is>
+          <t>Người Phê Duyệt Khóa</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3493,6 +3773,31 @@
           <t>Hạng A (Rất tốt)</t>
         </is>
       </c>
+      <c r="L5" s="99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="M5" s="100" t="inlineStr">
+        <is>
+          <t>Tháng 08/2026</t>
+        </is>
+      </c>
+      <c r="N5" s="101" t="inlineStr">
+        <is>
+          <t>ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="O5" s="99" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="P5" s="100" t="inlineStr">
+        <is>
+          <t>Quản đốc Trần Đức Minh</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3536,6 +3841,23 @@
           <t>Hạng A (Rất tốt)</t>
         </is>
       </c>
+      <c r="L6" s="99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="M6" s="100" t="inlineStr">
+        <is>
+          <t>Tháng 09/2026</t>
+        </is>
+      </c>
+      <c r="N6" s="102" t="inlineStr">
+        <is>
+          <t>ĐANG MỞ</t>
+        </is>
+      </c>
+      <c r="O6" s="99" t="inlineStr"/>
+      <c r="P6" s="100" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3579,6 +3901,23 @@
           <t>Hạng B (Đạt yêu cầu)</t>
         </is>
       </c>
+      <c r="L7" s="99" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="M7" s="100" t="inlineStr">
+        <is>
+          <t>Tháng 10/2026</t>
+        </is>
+      </c>
+      <c r="N7" s="102" t="inlineStr">
+        <is>
+          <t>ĐANG MỞ</t>
+        </is>
+      </c>
+      <c r="O7" s="99" t="inlineStr"/>
+      <c r="P7" s="100" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3622,6 +3961,23 @@
           <t>Hạng A (Rất tốt)</t>
         </is>
       </c>
+      <c r="L8" s="99" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="M8" s="100" t="inlineStr">
+        <is>
+          <t>Tháng 11/2026</t>
+        </is>
+      </c>
+      <c r="N8" s="102" t="inlineStr">
+        <is>
+          <t>ĐANG MỞ</t>
+        </is>
+      </c>
+      <c r="O8" s="99" t="inlineStr"/>
+      <c r="P8" s="100" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3665,6 +4021,23 @@
           <t>Hạng A (Rất tốt)</t>
         </is>
       </c>
+      <c r="L9" s="99" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="M9" s="100" t="inlineStr">
+        <is>
+          <t>Tháng 12/2026</t>
+        </is>
+      </c>
+      <c r="N9" s="102" t="inlineStr">
+        <is>
+          <t>ĐANG MỞ</t>
+        </is>
+      </c>
+      <c r="O9" s="99" t="inlineStr"/>
+      <c r="P9" s="100" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3737,9 +4110,983 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L3:P3"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54.43" customWidth="1" style="75" min="1" max="1"/>
+    <col width="15" customWidth="1" style="75" min="2" max="2"/>
+    <col width="22.29" customWidth="1" style="75" min="3" max="3"/>
+    <col width="28.43" customWidth="1" style="75" min="4" max="4"/>
+    <col width="14.86" customWidth="1" style="75" min="5" max="5"/>
+    <col width="16" customWidth="1" style="75" min="6" max="9"/>
+    <col width="16.14" customWidth="1" style="75" min="7" max="7"/>
+    <col width="18" customWidth="1" style="75" min="8" max="8"/>
+    <col width="26.86" customWidth="1" style="75" min="9" max="9"/>
+    <col width="23.71" customWidth="1" style="75" min="10" max="10"/>
+    <col width="30.43" customWidth="1" style="75" min="11" max="11"/>
+    <col width="22.29" customWidth="1" style="75" min="12" max="12"/>
+    <col width="31.14" customWidth="1" style="75" min="13" max="13"/>
+    <col width="10.86" customWidth="1" style="75" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1" s="75">
+      <c r="A1" s="103" t="inlineStr">
+        <is>
+          <t>BẢNG TRA CỨU LƯƠNG KHOÁN THEO THÁNG NĂM 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="104" t="n"/>
+      <c r="C1" s="104" t="n"/>
+      <c r="D1" s="104" t="n"/>
+      <c r="E1" s="104" t="n"/>
+      <c r="F1" s="104" t="n"/>
+      <c r="G1" s="104" t="n"/>
+      <c r="H1" s="104" t="n"/>
+      <c r="I1" s="104" t="n"/>
+      <c r="J1" s="104" t="n"/>
+      <c r="K1" s="104" t="n"/>
+      <c r="L1" s="104" t="n"/>
+      <c r="M1" s="104" t="n"/>
+      <c r="N1" s="104" t="n"/>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" s="75">
+      <c r="A2" s="105" t="inlineStr">
+        <is>
+          <t>Kỳ Lương:</t>
+        </is>
+      </c>
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
+        <is>
+          <t>Từ Ngày:</t>
+        </is>
+      </c>
+      <c r="D2" s="108" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
+        <is>
+          <t>Đến Ngày:</t>
+        </is>
+      </c>
+      <c r="F2" s="108" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G2" s="107" t="inlineStr">
+        <is>
+          <t>Trạng Thái Kỳ:</t>
+        </is>
+      </c>
+      <c r="H2" s="107" t="inlineStr">
+        <is>
+          <t>ĐÃ KHÓA SỔ</t>
+        </is>
+      </c>
+      <c r="I2" s="107" t="n"/>
+      <c r="J2" s="107" t="n"/>
+      <c r="K2" s="107" t="n"/>
+      <c r="L2" s="107" t="n"/>
+      <c r="M2" s="107" t="n"/>
+      <c r="N2" s="107" t="n"/>
+    </row>
+    <row r="3" ht="25.5" customHeight="1" s="75">
+      <c r="A3" s="109" t="inlineStr">
+        <is>
+          <t>Phân xưởng Gia công Cơ khí | Tra cứu lương khoán động theo kỳ: Chọn tháng tại B2 -&gt; Tự động đối soát 3 cấp</t>
+        </is>
+      </c>
+      <c r="B3" s="109" t="n"/>
+      <c r="C3" s="109" t="n"/>
+      <c r="D3" s="109" t="n"/>
+      <c r="E3" s="109" t="n"/>
+      <c r="F3" s="109" t="n"/>
+      <c r="G3" s="109" t="n"/>
+      <c r="H3" s="109" t="n"/>
+      <c r="I3" s="109" t="n"/>
+      <c r="J3" s="109" t="n"/>
+      <c r="K3" s="109" t="n"/>
+      <c r="L3" s="109" t="n"/>
+      <c r="M3" s="109" t="n"/>
+      <c r="N3" s="109" t="n"/>
+    </row>
+    <row r="4" ht="25.5" customHeight="1" s="75">
+      <c r="A4" s="110" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="110" t="inlineStr">
+        <is>
+          <t>Mã NV</t>
+        </is>
+      </c>
+      <c r="C4" s="110" t="inlineStr">
+        <is>
+          <t>Họ Và Tên Thợ Gia Công</t>
+        </is>
+      </c>
+      <c r="D4" s="110" t="inlineStr">
+        <is>
+          <t>Vị Trí / Máy Đảm Nhiệm</t>
+        </is>
+      </c>
+      <c r="E4" s="111" t="inlineStr">
+        <is>
+          <t>Số Ca Làm Việc</t>
+        </is>
+      </c>
+      <c r="F4" s="112" t="inlineStr">
+        <is>
+          <t>Tổng Giờ Máy (h)</t>
+        </is>
+      </c>
+      <c r="G4" s="113" t="inlineStr">
+        <is>
+          <t>Tổng SL Đạt (OK)</t>
+        </is>
+      </c>
+      <c r="H4" s="113" t="inlineStr">
+        <is>
+          <t>Tổng SL Hỏng (NG)</t>
+        </is>
+      </c>
+      <c r="I4" s="113" t="inlineStr">
+        <is>
+          <t>Tiền khoán phát sinh ban đầu</t>
+        </is>
+      </c>
+      <c r="J4" s="113" t="inlineStr">
+        <is>
+          <t>Tiền đủ điều kiện sau KCS</t>
+        </is>
+      </c>
+      <c r="K4" s="113" t="inlineStr">
+        <is>
+          <t>Tiền không được hưởng do lỗi thợ</t>
+        </is>
+      </c>
+      <c r="L4" s="110" t="inlineStr">
+        <is>
+          <t>Lương thực lĩnh đã khóa</t>
+        </is>
+      </c>
+      <c r="M4" s="110" t="inlineStr">
+        <is>
+          <t>Trạng Thái Chốt Lương</t>
+        </is>
+      </c>
+      <c r="N4" s="110" t="inlineStr">
+        <is>
+          <t>Ký Nhận</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1" s="75">
+      <c r="A5" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="114" t="inlineStr">
+        <is>
+          <t>NV01</t>
+        </is>
+      </c>
+      <c r="C5" s="115" t="inlineStr">
+        <is>
+          <t>Hoàng Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="D5" s="115" t="inlineStr">
+        <is>
+          <t>M01 - Máy tiện FUJI</t>
+        </is>
+      </c>
+      <c r="E5" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="119">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L5&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N5" s="115" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1" s="75">
+      <c r="A6" s="120" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="120" t="inlineStr">
+        <is>
+          <t>NV02</t>
+        </is>
+      </c>
+      <c r="C6" s="121" t="inlineStr">
+        <is>
+          <t>Nguyễn Trung Đông</t>
+        </is>
+      </c>
+      <c r="D6" s="121" t="inlineStr">
+        <is>
+          <t>M02 - Máy tiện OKUMA</t>
+        </is>
+      </c>
+      <c r="E6" s="122" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" s="123" t="n">
+        <v>104</v>
+      </c>
+      <c r="G6" s="124" t="n">
+        <v>70</v>
+      </c>
+      <c r="H6" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="124" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="J6" s="124" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="K6" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="124" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="M6" s="125">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L6&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N6" s="121" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" s="75">
+      <c r="A7" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="126" t="inlineStr">
+        <is>
+          <t>NV03</t>
+        </is>
+      </c>
+      <c r="C7" s="127" t="inlineStr">
+        <is>
+          <t>Phùng Đình Hùng</t>
+        </is>
+      </c>
+      <c r="D7" s="127" t="inlineStr">
+        <is>
+          <t>M03 - Máy tiện CNC1</t>
+        </is>
+      </c>
+      <c r="E7" s="128" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="129" t="n">
+        <v>56</v>
+      </c>
+      <c r="G7" s="130" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="130" t="n">
+        <v>525000</v>
+      </c>
+      <c r="J7" s="130" t="n">
+        <v>350000</v>
+      </c>
+      <c r="K7" s="130" t="n">
+        <v>175000</v>
+      </c>
+      <c r="L7" s="130" t="n">
+        <v>350000</v>
+      </c>
+      <c r="M7" s="131">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L7&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N7" s="127" t="n"/>
+    </row>
+    <row r="8" ht="19.5" customHeight="1" s="75">
+      <c r="A8" s="120" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="120" t="inlineStr">
+        <is>
+          <t>NV04</t>
+        </is>
+      </c>
+      <c r="C8" s="121" t="inlineStr">
+        <is>
+          <t>Vũ Tiến Thuận</t>
+        </is>
+      </c>
+      <c r="D8" s="121" t="inlineStr">
+        <is>
+          <t>M04 - Máy tiện CNC2</t>
+        </is>
+      </c>
+      <c r="E8" s="122" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="123" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" s="124" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="124" t="n">
+        <v>910000</v>
+      </c>
+      <c r="J8" s="124" t="n">
+        <v>910000</v>
+      </c>
+      <c r="K8" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="124" t="n">
+        <v>910000</v>
+      </c>
+      <c r="M8" s="125">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L8&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N8" s="121" t="n"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1" s="75">
+      <c r="A9" s="126" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="126" t="inlineStr">
+        <is>
+          <t>NV05</t>
+        </is>
+      </c>
+      <c r="C9" s="127" t="inlineStr">
+        <is>
+          <t>Nguyễn Mạnh Hà</t>
+        </is>
+      </c>
+      <c r="D9" s="127" t="inlineStr">
+        <is>
+          <t>M05 - Máy tiện T630</t>
+        </is>
+      </c>
+      <c r="E9" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="131">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L9&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N9" s="127" t="n"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="1" s="75">
+      <c r="A10" s="120" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="120" t="inlineStr">
+        <is>
+          <t>NV06</t>
+        </is>
+      </c>
+      <c r="C10" s="121" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thanh</t>
+        </is>
+      </c>
+      <c r="D10" s="121" t="inlineStr">
+        <is>
+          <t>M06 - Máy tiện T1516</t>
+        </is>
+      </c>
+      <c r="E10" s="122" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="123" t="n">
+        <v>128</v>
+      </c>
+      <c r="G10" s="124" t="n">
+        <v>509</v>
+      </c>
+      <c r="H10" s="124" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="124" t="n">
+        <v>17815000</v>
+      </c>
+      <c r="J10" s="124" t="n">
+        <v>9625000</v>
+      </c>
+      <c r="K10" s="124" t="n">
+        <v>8190000</v>
+      </c>
+      <c r="L10" s="124" t="n">
+        <v>9625000</v>
+      </c>
+      <c r="M10" s="125">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L10&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N10" s="121" t="n"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" s="75">
+      <c r="A11" s="126" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="126" t="inlineStr">
+        <is>
+          <t>NV07</t>
+        </is>
+      </c>
+      <c r="C11" s="127" t="inlineStr">
+        <is>
+          <t>Phùng Gia Phúc</t>
+        </is>
+      </c>
+      <c r="D11" s="127" t="inlineStr">
+        <is>
+          <t>M07 - Máy Phay OKK1</t>
+        </is>
+      </c>
+      <c r="E11" s="128" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="129" t="n">
+        <v>96</v>
+      </c>
+      <c r="G11" s="130" t="n">
+        <v>265</v>
+      </c>
+      <c r="H11" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="130" t="n">
+        <v>9402600</v>
+      </c>
+      <c r="J11" s="130" t="n">
+        <v>9402600</v>
+      </c>
+      <c r="K11" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="130" t="n">
+        <v>9402600</v>
+      </c>
+      <c r="M11" s="131">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L11&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N11" s="127" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1" s="75">
+      <c r="A12" s="120" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="120" t="inlineStr">
+        <is>
+          <t>NV08</t>
+        </is>
+      </c>
+      <c r="C12" s="121" t="inlineStr">
+        <is>
+          <t>Trần Văn Dũng</t>
+        </is>
+      </c>
+      <c r="D12" s="121" t="inlineStr">
+        <is>
+          <t>M08 - Máy Phay OKK2</t>
+        </is>
+      </c>
+      <c r="E12" s="122" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="123" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" s="124" t="n">
+        <v>196</v>
+      </c>
+      <c r="H12" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="124" t="n">
+        <v>7136536</v>
+      </c>
+      <c r="J12" s="124" t="n">
+        <v>7136536</v>
+      </c>
+      <c r="K12" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="124" t="n">
+        <v>7136536</v>
+      </c>
+      <c r="M12" s="125">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L12&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N12" s="121" t="n"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" s="75">
+      <c r="A13" s="126" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="126" t="inlineStr">
+        <is>
+          <t>NV09</t>
+        </is>
+      </c>
+      <c r="C13" s="127" t="inlineStr">
+        <is>
+          <t>Trần Đăng Ninh</t>
+        </is>
+      </c>
+      <c r="D13" s="127" t="inlineStr">
+        <is>
+          <t>M09 - Máy Phay OKK3</t>
+        </is>
+      </c>
+      <c r="E13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="131">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L13&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N13" s="127" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" s="75">
+      <c r="A14" s="120" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="120" t="inlineStr">
+        <is>
+          <t>NV10</t>
+        </is>
+      </c>
+      <c r="C14" s="121" t="inlineStr">
+        <is>
+          <t>Phạm Văn Tráng</t>
+        </is>
+      </c>
+      <c r="D14" s="121" t="inlineStr">
+        <is>
+          <t>M10 - Máy Phay CNC1</t>
+        </is>
+      </c>
+      <c r="E14" s="122" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" s="123" t="n">
+        <v>144</v>
+      </c>
+      <c r="G14" s="124" t="n">
+        <v>294</v>
+      </c>
+      <c r="H14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="124" t="n">
+        <v>11039600</v>
+      </c>
+      <c r="J14" s="124" t="n">
+        <v>11039600</v>
+      </c>
+      <c r="K14" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="124" t="n">
+        <v>11039600</v>
+      </c>
+      <c r="M14" s="125">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L14&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N14" s="121" t="n"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1" s="75">
+      <c r="A15" s="126" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="126" t="inlineStr">
+        <is>
+          <t>NV11</t>
+        </is>
+      </c>
+      <c r="C15" s="127" t="inlineStr">
+        <is>
+          <t>Phùng Công Thắng</t>
+        </is>
+      </c>
+      <c r="D15" s="127" t="inlineStr">
+        <is>
+          <t>M11 - Máy Phay CNC2</t>
+        </is>
+      </c>
+      <c r="E15" s="128" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="129" t="n">
+        <v>104</v>
+      </c>
+      <c r="G15" s="130" t="n">
+        <v>464</v>
+      </c>
+      <c r="H15" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="130" t="n">
+        <v>16240000</v>
+      </c>
+      <c r="J15" s="130" t="n">
+        <v>15820000</v>
+      </c>
+      <c r="K15" s="130" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L15" s="130" t="n">
+        <v>15820000</v>
+      </c>
+      <c r="M15" s="131">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L15&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N15" s="127" t="n"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" s="75">
+      <c r="A16" s="120" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="120" t="inlineStr">
+        <is>
+          <t>NV12</t>
+        </is>
+      </c>
+      <c r="C16" s="121" t="inlineStr">
+        <is>
+          <t>Phạm Ngọc Sam</t>
+        </is>
+      </c>
+      <c r="D16" s="121" t="inlineStr">
+        <is>
+          <t>M12 - Máy Phay OIGO</t>
+        </is>
+      </c>
+      <c r="E16" s="122" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" s="123" t="n">
+        <v>136</v>
+      </c>
+      <c r="G16" s="124" t="n">
+        <v>98</v>
+      </c>
+      <c r="H16" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="124" t="n">
+        <v>3430000</v>
+      </c>
+      <c r="J16" s="124" t="n">
+        <v>595000</v>
+      </c>
+      <c r="K16" s="124" t="n">
+        <v>2835000</v>
+      </c>
+      <c r="L16" s="124" t="n">
+        <v>595000</v>
+      </c>
+      <c r="M16" s="125">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L16&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N16" s="121" t="n"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" s="75">
+      <c r="A17" s="126" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="126" t="inlineStr">
+        <is>
+          <t>NV13</t>
+        </is>
+      </c>
+      <c r="C17" s="127" t="inlineStr">
+        <is>
+          <t>Trần Văn Quỳnh</t>
+        </is>
+      </c>
+      <c r="D17" s="127" t="inlineStr">
+        <is>
+          <t>M13 - Máy Phay YM</t>
+        </is>
+      </c>
+      <c r="E17" s="128" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="129" t="n">
+        <v>56</v>
+      </c>
+      <c r="G17" s="130" t="n">
+        <v>139</v>
+      </c>
+      <c r="H17" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="130" t="n">
+        <v>5390256</v>
+      </c>
+      <c r="J17" s="130" t="n">
+        <v>5390256</v>
+      </c>
+      <c r="K17" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="130" t="n">
+        <v>5390256</v>
+      </c>
+      <c r="M17" s="131">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L17&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N17" s="127" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" s="75">
+      <c r="A18" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="120" t="inlineStr">
+        <is>
+          <t>NV14</t>
+        </is>
+      </c>
+      <c r="C18" s="121" t="inlineStr">
+        <is>
+          <t>Đinh Văn Nhận</t>
+        </is>
+      </c>
+      <c r="D18" s="121" t="inlineStr">
+        <is>
+          <t>M15 - Máy Khoan cần Yoshida</t>
+        </is>
+      </c>
+      <c r="E18" s="122" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="123" t="n">
+        <v>72</v>
+      </c>
+      <c r="G18" s="124" t="n">
+        <v>160</v>
+      </c>
+      <c r="H18" s="124" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="124" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J18" s="124" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="K18" s="124" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="L18" s="124" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="M18" s="125">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L18&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N18" s="121" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1" s="75">
+      <c r="A19" s="132" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="132" t="inlineStr">
+        <is>
+          <t>NV15</t>
+        </is>
+      </c>
+      <c r="C19" s="133" t="inlineStr">
+        <is>
+          <t>Đặng Ngọc Long</t>
+        </is>
+      </c>
+      <c r="D19" s="133" t="inlineStr">
+        <is>
+          <t>M16 - Máy Cắt Dây DK7745</t>
+        </is>
+      </c>
+      <c r="E19" s="134" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" s="135" t="n">
+        <v>128</v>
+      </c>
+      <c r="G19" s="136" t="n">
+        <v>136</v>
+      </c>
+      <c r="H19" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="136" t="n">
+        <v>4760000</v>
+      </c>
+      <c r="J19" s="136" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="K19" s="136" t="n">
+        <v>3010000</v>
+      </c>
+      <c r="L19" s="136" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="M19" s="137">
+        <f>IF($H$2="ĐÃ KHÓA SỔ", "🔒 ĐÃ KHÓA SỔ", IF(L19&gt;0, "CHỜ KHÓA SỔ", "KỲ ĐANG MỞ"))</f>
+        <v/>
+      </c>
+      <c r="N19" s="133" t="n"/>
+    </row>
+    <row r="20" ht="22.5" customHeight="1" s="75">
+      <c r="A20" s="138" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG QUỸ LƯƠNG KHOÁN (15 THỢ)</t>
+        </is>
+      </c>
+      <c r="B20" s="138" t="n"/>
+      <c r="C20" s="139" t="n"/>
+      <c r="D20" s="139" t="n"/>
+      <c r="E20" s="140">
+        <f>SUM(E5:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="141">
+        <f>SUM(F5:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="142">
+        <f>SUM(G5:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="142">
+        <f>SUM(H5:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="142">
+        <f>SUM(I5:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="142">
+        <f>SUM(J5:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="142">
+        <f>SUM(K5:K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="142">
+        <f>SUM(L5:L19)</f>
+        <v/>
+      </c>
+      <c r="M20" s="138" t="inlineStr">
+        <is>
+          <t>🔒 KHỚP 100% KỲ ĐÃ KHÓA</t>
+        </is>
+      </c>
+      <c r="N20" s="139" t="n"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10136,18 +11483,16 @@
         <v>15</v>
       </c>
       <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
         <v>15</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H19" s="6">
-        <f>MAX(0, F19-G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="6">
-        <f>MAX(0, E19-G19)</f>
-        <v/>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -37026,7 +38371,7 @@
         <v>37200</v>
       </c>
       <c r="M216" s="62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N216" s="44" t="n">
         <v>0</v>
@@ -37053,7 +38398,7 @@
       </c>
       <c r="T216" s="41" t="inlineStr">
         <is>
-          <t>Đang gia công dở dang, chuyển ca sau</t>
+          <t>Đang gia công dở dang, chuyển ca sau | ⚠️ ĐÃ HỦY (BẢN GHI GỬI LẶP LÚC 01:52:29)</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
@@ -37128,7 +38473,7 @@
         <v>37200</v>
       </c>
       <c r="M217" s="67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N217" s="50" t="n">
         <v>0</v>
@@ -37155,7 +38500,7 @@
       </c>
       <c r="T217" s="47" t="inlineStr">
         <is>
-          <t>Đang gia công dở dang, chuyển ca sau</t>
+          <t>Đang gia công dở dang, chuyển ca sau | ⚠️ ĐÃ HỦY (BẢN GHI GỬI LẶP LÚC 01:52:29)</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
